--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH261"/>
+  <dimension ref="A1:AH262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28557,6 +28557,114 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="n">
+        <v>376.06</v>
+      </c>
+      <c r="C262" t="n">
+        <v>371.98</v>
+      </c>
+      <c r="D262" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="E262" t="n">
+        <v>366.27</v>
+      </c>
+      <c r="F262" t="n">
+        <v>366.34</v>
+      </c>
+      <c r="G262" t="n">
+        <v>365.99</v>
+      </c>
+      <c r="H262" t="n">
+        <v>367.03</v>
+      </c>
+      <c r="I262" t="n">
+        <v>375.54</v>
+      </c>
+      <c r="J262" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="K262" t="n">
+        <v>381.39</v>
+      </c>
+      <c r="L262" t="n">
+        <v>382.08</v>
+      </c>
+      <c r="M262" t="n">
+        <v>383.67</v>
+      </c>
+      <c r="N262" t="n">
+        <v>378.03</v>
+      </c>
+      <c r="O262" t="n">
+        <v>377.6</v>
+      </c>
+      <c r="P262" t="n">
+        <v>374.89</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>370.35</v>
+      </c>
+      <c r="R262" t="n">
+        <v>370.2</v>
+      </c>
+      <c r="S262" t="n">
+        <v>372.61</v>
+      </c>
+      <c r="T262" t="n">
+        <v>375.88</v>
+      </c>
+      <c r="U262" t="n">
+        <v>374.41</v>
+      </c>
+      <c r="V262" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="W262" t="n">
+        <v>376.81</v>
+      </c>
+      <c r="X262" t="n">
+        <v>377.7</v>
+      </c>
+      <c r="Y262" t="n">
+        <v>377.53</v>
+      </c>
+      <c r="Z262" t="n">
+        <v>377.77</v>
+      </c>
+      <c r="AA262" t="n">
+        <v>377.77</v>
+      </c>
+      <c r="AB262" t="n">
+        <v>380.27</v>
+      </c>
+      <c r="AC262" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="AD262" t="n">
+        <v>383.98</v>
+      </c>
+      <c r="AE262" t="n">
+        <v>380.51</v>
+      </c>
+      <c r="AF262" t="n">
+        <v>392.31</v>
+      </c>
+      <c r="AG262" t="n">
+        <v>373.71</v>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28568,7 +28676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B267"/>
+  <dimension ref="A1:B268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31241,6 +31349,16 @@
       </c>
       <c r="B267" t="n">
         <v>0.36</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -31409,28 +31527,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1873692348692315</v>
+        <v>-0.1869594787275971</v>
       </c>
       <c r="J2" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K2" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03711168559816447</v>
+        <v>0.03725020944161184</v>
       </c>
       <c r="M2" t="n">
-        <v>5.626613610277676</v>
+        <v>5.606485407922931</v>
       </c>
       <c r="N2" t="n">
-        <v>48.28471719057065</v>
+        <v>48.09718138546668</v>
       </c>
       <c r="O2" t="n">
-        <v>6.948720543421692</v>
+        <v>6.935213146361594</v>
       </c>
       <c r="P2" t="n">
-        <v>380.4769727819315</v>
+        <v>380.4725631008428</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31487,28 +31605,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2683559539221736</v>
+        <v>-0.2648794250780183</v>
       </c>
       <c r="J3" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K3" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07332566479028235</v>
+        <v>0.0720127059908281</v>
       </c>
       <c r="M3" t="n">
-        <v>5.490558803470716</v>
+        <v>5.48771381488867</v>
       </c>
       <c r="N3" t="n">
-        <v>48.93435359101638</v>
+        <v>48.82305240839349</v>
       </c>
       <c r="O3" t="n">
-        <v>6.995309399234345</v>
+        <v>6.987349455150607</v>
       </c>
       <c r="P3" t="n">
-        <v>374.5185384020335</v>
+        <v>374.4814859185254</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31565,28 +31683,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4001726679623065</v>
+        <v>-0.3971887357314901</v>
       </c>
       <c r="J4" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K4" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1070735086881813</v>
+        <v>0.1063578146002186</v>
       </c>
       <c r="M4" t="n">
-        <v>6.523875258936875</v>
+        <v>6.514851212918247</v>
       </c>
       <c r="N4" t="n">
-        <v>70.79073287533339</v>
+        <v>70.57128725343665</v>
       </c>
       <c r="O4" t="n">
-        <v>8.413722890334183</v>
+        <v>8.400671833456933</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0969354279925</v>
+        <v>371.0648231831938</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31643,28 +31761,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6278537194193752</v>
+        <v>-0.6293691537959664</v>
       </c>
       <c r="J5" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K5" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1624633753563937</v>
+        <v>0.1642345353185292</v>
       </c>
       <c r="M5" t="n">
-        <v>8.035171803591926</v>
+        <v>8.010066954288771</v>
       </c>
       <c r="N5" t="n">
-        <v>107.1677241874896</v>
+        <v>106.7620962246082</v>
       </c>
       <c r="O5" t="n">
-        <v>10.35218451282093</v>
+        <v>10.33257452064142</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7709350267727</v>
+        <v>384.7873189242916</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31721,28 +31839,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5836044735683634</v>
+        <v>-0.5850277533009046</v>
       </c>
       <c r="J6" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K6" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1108145594075861</v>
+        <v>0.1121066817367934</v>
       </c>
       <c r="M6" t="n">
-        <v>9.398820715064442</v>
+        <v>9.368704359150225</v>
       </c>
       <c r="N6" t="n">
-        <v>145.2944352852699</v>
+        <v>144.7421199422733</v>
       </c>
       <c r="O6" t="n">
-        <v>12.05381413849035</v>
+        <v>12.03088192703566</v>
       </c>
       <c r="P6" t="n">
-        <v>383.5698538212469</v>
+        <v>383.5851251189397</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31799,28 +31917,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6804880431072526</v>
+        <v>-0.6801260551620667</v>
       </c>
       <c r="J7" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K7" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05095824235046398</v>
+        <v>0.05130791483035513</v>
       </c>
       <c r="M7" t="n">
-        <v>17.06256450095109</v>
+        <v>16.99701035167684</v>
       </c>
       <c r="N7" t="n">
-        <v>455.4862511807398</v>
+        <v>453.7008672968728</v>
       </c>
       <c r="O7" t="n">
-        <v>21.34212386761776</v>
+        <v>21.30025509933796</v>
       </c>
       <c r="P7" t="n">
-        <v>383.4720656662126</v>
+        <v>383.4681561039909</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31881,28 +31999,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4719385763838083</v>
+        <v>0.4646503843219361</v>
       </c>
       <c r="J8" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K8" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03188689470525108</v>
+        <v>0.03115922519878711</v>
       </c>
       <c r="M8" t="n">
-        <v>14.99617923767102</v>
+        <v>14.96886974580191</v>
       </c>
       <c r="N8" t="n">
-        <v>360.5846739104699</v>
+        <v>359.4972830796773</v>
       </c>
       <c r="O8" t="n">
-        <v>18.98906722065278</v>
+        <v>18.96041357881408</v>
       </c>
       <c r="P8" t="n">
-        <v>363.9454334635097</v>
+        <v>364.0239066021311</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -31963,28 +32081,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6534325134914677</v>
+        <v>0.6444814138947415</v>
       </c>
       <c r="J9" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K9" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1225968027925126</v>
+        <v>0.1201857176776623</v>
       </c>
       <c r="M9" t="n">
-        <v>10.1898723351389</v>
+        <v>10.19003886899285</v>
       </c>
       <c r="N9" t="n">
-        <v>166.5287926123912</v>
+        <v>166.4090057136357</v>
       </c>
       <c r="O9" t="n">
-        <v>12.9046035434023</v>
+        <v>12.89996146171126</v>
       </c>
       <c r="P9" t="n">
-        <v>370.0437319184035</v>
+        <v>370.1384634875504</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32045,28 +32163,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4285127038295701</v>
+        <v>0.4230846596414497</v>
       </c>
       <c r="J10" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K10" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1111325234390155</v>
+        <v>0.109195909427798</v>
       </c>
       <c r="M10" t="n">
-        <v>7.031464075862181</v>
+        <v>7.029689770009086</v>
       </c>
       <c r="N10" t="n">
-        <v>79.77806061906193</v>
+        <v>79.66537856506058</v>
       </c>
       <c r="O10" t="n">
-        <v>8.931856504616604</v>
+        <v>8.92554640148493</v>
       </c>
       <c r="P10" t="n">
-        <v>372.9089712581776</v>
+        <v>372.9663069369802</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32123,28 +32241,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3726944603224685</v>
+        <v>0.3708437169321578</v>
       </c>
       <c r="J11" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K11" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1129053792907835</v>
+        <v>0.1126982981602288</v>
       </c>
       <c r="M11" t="n">
-        <v>6.159911962264061</v>
+        <v>6.1439241827499</v>
       </c>
       <c r="N11" t="n">
-        <v>57.99772469122803</v>
+        <v>57.79407305960007</v>
       </c>
       <c r="O11" t="n">
-        <v>7.615623723059591</v>
+        <v>7.602241318164011</v>
       </c>
       <c r="P11" t="n">
-        <v>373.9567841210749</v>
+        <v>373.9766456542228</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32201,28 +32319,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3984681134809898</v>
+        <v>0.3984632161164965</v>
       </c>
       <c r="J12" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K12" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1323198276525178</v>
+        <v>0.1332691733117016</v>
       </c>
       <c r="M12" t="n">
-        <v>6.060239413886432</v>
+        <v>6.036681480705899</v>
       </c>
       <c r="N12" t="n">
-        <v>55.33140059430396</v>
+        <v>55.11610346991776</v>
       </c>
       <c r="O12" t="n">
-        <v>7.438507954845781</v>
+        <v>7.4240220547839</v>
       </c>
       <c r="P12" t="n">
-        <v>371.5816725817047</v>
+        <v>371.5817251385138</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32279,28 +32397,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2894199971643605</v>
+        <v>0.2898024515677483</v>
       </c>
       <c r="J13" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K13" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09921257236250802</v>
+        <v>0.1001897121080753</v>
       </c>
       <c r="M13" t="n">
-        <v>5.08946377995416</v>
+        <v>5.071724194456687</v>
       </c>
       <c r="N13" t="n">
-        <v>40.41684839084175</v>
+        <v>40.26052474702025</v>
       </c>
       <c r="O13" t="n">
-        <v>6.357424666548692</v>
+        <v>6.345118182273696</v>
       </c>
       <c r="P13" t="n">
-        <v>375.5464435754424</v>
+        <v>375.5423392080567</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32357,28 +32475,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1395913334650819</v>
+        <v>0.1367570795996907</v>
       </c>
       <c r="J14" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K14" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03567078695540449</v>
+        <v>0.03449879715759241</v>
       </c>
       <c r="M14" t="n">
-        <v>4.298133616319439</v>
+        <v>4.292381344335165</v>
       </c>
       <c r="N14" t="n">
-        <v>28.16629264911717</v>
+        <v>28.10915521569409</v>
       </c>
       <c r="O14" t="n">
-        <v>5.307192539292047</v>
+        <v>5.301806787850166</v>
       </c>
       <c r="P14" t="n">
-        <v>378.0318062025229</v>
+        <v>378.0620672962912</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32435,28 +32553,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2921261816169944</v>
+        <v>0.2890798939710978</v>
       </c>
       <c r="J15" t="n">
+        <v>261</v>
+      </c>
+      <c r="K15" t="n">
         <v>260</v>
       </c>
-      <c r="K15" t="n">
-        <v>259</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1713060110273436</v>
+        <v>0.1691120471416265</v>
       </c>
       <c r="M15" t="n">
-        <v>3.790844685469211</v>
+        <v>3.787905632181781</v>
       </c>
       <c r="N15" t="n">
-        <v>22.55178524658499</v>
+        <v>22.52699620301343</v>
       </c>
       <c r="O15" t="n">
-        <v>4.748871997283669</v>
+        <v>4.746261286846041</v>
       </c>
       <c r="P15" t="n">
-        <v>373.93888433885</v>
+        <v>373.9709021992841</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32513,28 +32631,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1826197500310573</v>
+        <v>0.179192792558631</v>
       </c>
       <c r="J16" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K16" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L16" t="n">
-        <v>0.09228731943287782</v>
+        <v>0.08947327110670644</v>
       </c>
       <c r="M16" t="n">
-        <v>3.540361838621362</v>
+        <v>3.541587398262191</v>
       </c>
       <c r="N16" t="n">
-        <v>17.88387982081658</v>
+        <v>17.89346340509092</v>
       </c>
       <c r="O16" t="n">
-        <v>4.228933650557382</v>
+        <v>4.230066595822213</v>
       </c>
       <c r="P16" t="n">
-        <v>374.6197280280198</v>
+        <v>374.6557447738422</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32591,28 +32709,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2248085697303785</v>
+        <v>0.2189310497837067</v>
       </c>
       <c r="J17" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K17" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1274929151202377</v>
+        <v>0.1212920779648021</v>
       </c>
       <c r="M17" t="n">
-        <v>3.474362845693771</v>
+        <v>3.489170443881513</v>
       </c>
       <c r="N17" t="n">
-        <v>18.85682279943094</v>
+        <v>19.01431895716643</v>
       </c>
       <c r="O17" t="n">
-        <v>4.342444334638147</v>
+        <v>4.360541131232043</v>
       </c>
       <c r="P17" t="n">
-        <v>372.2085956815652</v>
+        <v>372.2703674262361</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32669,28 +32787,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1659018219980095</v>
+        <v>0.1596512425625559</v>
       </c>
       <c r="J18" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K18" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L18" t="n">
-        <v>0.06728008960303711</v>
+        <v>0.0623677291501844</v>
       </c>
       <c r="M18" t="n">
-        <v>3.67673769070529</v>
+        <v>3.684356040497691</v>
       </c>
       <c r="N18" t="n">
-        <v>20.80304371389406</v>
+        <v>20.98317347379895</v>
       </c>
       <c r="O18" t="n">
-        <v>4.561035377399967</v>
+        <v>4.580739402519963</v>
       </c>
       <c r="P18" t="n">
-        <v>374.1081621486161</v>
+        <v>374.1738546856786</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32747,28 +32865,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1709984237549299</v>
+        <v>0.1647031596905636</v>
       </c>
       <c r="J19" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K19" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L19" t="n">
-        <v>0.06668975390953813</v>
+        <v>0.06196053361432097</v>
       </c>
       <c r="M19" t="n">
-        <v>3.738287950697921</v>
+        <v>3.740070028806902</v>
       </c>
       <c r="N19" t="n">
-        <v>22.31058803594481</v>
+        <v>22.48867009924877</v>
       </c>
       <c r="O19" t="n">
-        <v>4.723408518850007</v>
+        <v>4.742222063468641</v>
       </c>
       <c r="P19" t="n">
-        <v>376.4429869540991</v>
+        <v>376.5091491190851</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32825,28 +32943,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1328890352158835</v>
+        <v>0.1289851583176413</v>
       </c>
       <c r="J20" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K20" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0427102674976757</v>
+        <v>0.04047302565782407</v>
       </c>
       <c r="M20" t="n">
-        <v>3.677439677967151</v>
+        <v>3.677142518450611</v>
       </c>
       <c r="N20" t="n">
-        <v>21.57989316295825</v>
+        <v>21.5985675112905</v>
       </c>
       <c r="O20" t="n">
-        <v>4.645416360559971</v>
+        <v>4.647425901646039</v>
       </c>
       <c r="P20" t="n">
-        <v>377.5449745418442</v>
+        <v>377.5860036305029</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -32903,28 +33021,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1775185872116862</v>
+        <v>0.1738730049091698</v>
       </c>
       <c r="J21" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K21" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L21" t="n">
-        <v>0.07233121008373578</v>
+        <v>0.06986675823333588</v>
       </c>
       <c r="M21" t="n">
-        <v>3.672958412179384</v>
+        <v>3.675895702246787</v>
       </c>
       <c r="N21" t="n">
-        <v>22.0350867487922</v>
+        <v>22.03904860951248</v>
       </c>
       <c r="O21" t="n">
-        <v>4.694154529709498</v>
+        <v>4.694576510135124</v>
       </c>
       <c r="P21" t="n">
-        <v>374.5623600096208</v>
+        <v>374.6006744655838</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -32981,28 +33099,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2346582646821686</v>
+        <v>0.2303236292828086</v>
       </c>
       <c r="J22" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K22" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1048940156832308</v>
+        <v>0.1017466939196349</v>
       </c>
       <c r="M22" t="n">
-        <v>4.093263255201168</v>
+        <v>4.099006271683802</v>
       </c>
       <c r="N22" t="n">
-        <v>25.61859700939828</v>
+        <v>25.64539889584213</v>
       </c>
       <c r="O22" t="n">
-        <v>5.061481700984237</v>
+        <v>5.064128641320452</v>
       </c>
       <c r="P22" t="n">
-        <v>373.6671686363642</v>
+        <v>373.7127249243156</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33059,28 +33177,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2046048108011707</v>
+        <v>0.2006729397518565</v>
       </c>
       <c r="J23" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K23" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08748783689176376</v>
+        <v>0.08473881986431364</v>
       </c>
       <c r="M23" t="n">
-        <v>3.994098206808379</v>
+        <v>3.998315644775991</v>
       </c>
       <c r="N23" t="n">
-        <v>23.80578729919274</v>
+        <v>23.81739214754613</v>
       </c>
       <c r="O23" t="n">
-        <v>4.879117471345893</v>
+        <v>4.880306562865301</v>
       </c>
       <c r="P23" t="n">
-        <v>376.6308641560757</v>
+        <v>376.6721874585469</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33137,28 +33255,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1878170378995762</v>
+        <v>0.1849908104675219</v>
       </c>
       <c r="J24" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K24" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06492093365325224</v>
+        <v>0.06347628798607874</v>
       </c>
       <c r="M24" t="n">
-        <v>4.215979266462874</v>
+        <v>4.213387093794736</v>
       </c>
       <c r="N24" t="n">
-        <v>27.70087167530648</v>
+        <v>27.64785966823055</v>
       </c>
       <c r="O24" t="n">
-        <v>5.263161756521121</v>
+        <v>5.258123207783415</v>
       </c>
       <c r="P24" t="n">
-        <v>376.4964336226886</v>
+        <v>376.5261367969695</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33215,28 +33333,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1802147691008305</v>
+        <v>0.1775251175849696</v>
       </c>
       <c r="J25" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K25" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06249347740146516</v>
+        <v>0.06111977709075189</v>
       </c>
       <c r="M25" t="n">
-        <v>4.088015545632503</v>
+        <v>4.08466090545524</v>
       </c>
       <c r="N25" t="n">
-        <v>26.56319131095167</v>
+        <v>26.50952813946149</v>
       </c>
       <c r="O25" t="n">
-        <v>5.153949098599216</v>
+        <v>5.14874044203643</v>
       </c>
       <c r="P25" t="n">
-        <v>376.3458885244479</v>
+        <v>376.3741563088534</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -33293,28 +33411,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1563009281970073</v>
+        <v>0.1512089577395586</v>
       </c>
       <c r="J26" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K26" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05642169186154633</v>
+        <v>0.05302005812297261</v>
       </c>
       <c r="M26" t="n">
-        <v>3.738139396245392</v>
+        <v>3.74713799674202</v>
       </c>
       <c r="N26" t="n">
-        <v>22.27485274983733</v>
+        <v>22.36194478430541</v>
       </c>
       <c r="O26" t="n">
-        <v>4.719624217015305</v>
+        <v>4.728841801573131</v>
       </c>
       <c r="P26" t="n">
-        <v>380.3940037116363</v>
+        <v>380.4475194634881</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -33371,28 +33489,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1185727561811486</v>
+        <v>0.1139127836969717</v>
       </c>
       <c r="J27" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K27" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L27" t="n">
-        <v>0.03110095745219088</v>
+        <v>0.02883345362821843</v>
       </c>
       <c r="M27" t="n">
-        <v>3.92948083289129</v>
+        <v>3.935114390475948</v>
       </c>
       <c r="N27" t="n">
-        <v>23.8800087520114</v>
+        <v>23.93293323639565</v>
       </c>
       <c r="O27" t="n">
-        <v>4.886717584638118</v>
+        <v>4.892129723995026</v>
       </c>
       <c r="P27" t="n">
-        <v>380.8230080598761</v>
+        <v>380.8719835857915</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -33449,28 +33567,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1702824179913354</v>
+        <v>0.1651854621641731</v>
       </c>
       <c r="J28" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K28" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04957617262464087</v>
+        <v>0.04690085452644199</v>
       </c>
       <c r="M28" t="n">
-        <v>4.522119806871446</v>
+        <v>4.524352498650936</v>
       </c>
       <c r="N28" t="n">
-        <v>30.30706087122988</v>
+        <v>30.36371597989458</v>
       </c>
       <c r="O28" t="n">
-        <v>5.505184907996268</v>
+        <v>5.510328119077355</v>
       </c>
       <c r="P28" t="n">
-        <v>382.5335726592921</v>
+        <v>382.5871408065398</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -33527,28 +33645,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2080423747383287</v>
+        <v>0.2019932208379856</v>
       </c>
       <c r="J29" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K29" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L29" t="n">
-        <v>0.07945215046953458</v>
+        <v>0.07519314031345825</v>
       </c>
       <c r="M29" t="n">
-        <v>4.317235173693913</v>
+        <v>4.328709658861087</v>
       </c>
       <c r="N29" t="n">
-        <v>27.340358207919</v>
+        <v>27.47896420243538</v>
       </c>
       <c r="O29" t="n">
-        <v>5.22880083842548</v>
+        <v>5.24203817254657</v>
       </c>
       <c r="P29" t="n">
-        <v>386.5165619841002</v>
+        <v>386.5801375727154</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -33605,28 +33723,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2338871430990194</v>
+        <v>0.2289186363171574</v>
       </c>
       <c r="J30" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K30" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1336779644072041</v>
+        <v>0.1287498501724427</v>
       </c>
       <c r="M30" t="n">
-        <v>3.508260513627308</v>
+        <v>3.512954789727684</v>
       </c>
       <c r="N30" t="n">
-        <v>19.32823154302146</v>
+        <v>19.41835265435088</v>
       </c>
       <c r="O30" t="n">
-        <v>4.396388465891232</v>
+        <v>4.406625994380608</v>
       </c>
       <c r="P30" t="n">
-        <v>384.3943345192462</v>
+        <v>384.4465526886628</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -33683,28 +33801,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1793466326515994</v>
+        <v>0.1736725671971746</v>
       </c>
       <c r="J31" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K31" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L31" t="n">
-        <v>0.07495740470029699</v>
+        <v>0.07050880414637306</v>
       </c>
       <c r="M31" t="n">
-        <v>3.798996801035205</v>
+        <v>3.809187731406042</v>
       </c>
       <c r="N31" t="n">
-        <v>21.64180739657602</v>
+        <v>21.77300286913616</v>
       </c>
       <c r="O31" t="n">
-        <v>4.652075600909342</v>
+        <v>4.666155041266435</v>
       </c>
       <c r="P31" t="n">
-        <v>383.3044696387362</v>
+        <v>383.3641031109622</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -33761,28 +33879,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2189403861744382</v>
+        <v>0.2124902030946642</v>
       </c>
       <c r="J32" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K32" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0987566994842104</v>
+        <v>0.09327373840660025</v>
       </c>
       <c r="M32" t="n">
-        <v>3.79329252127207</v>
+        <v>3.808351906988444</v>
       </c>
       <c r="N32" t="n">
-        <v>23.84993093925031</v>
+        <v>24.03524670977357</v>
       </c>
       <c r="O32" t="n">
-        <v>4.883639108211243</v>
+        <v>4.90257551800822</v>
       </c>
       <c r="P32" t="n">
-        <v>395.0907143510604</v>
+        <v>395.1585046888048</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -33839,28 +33957,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1439616847855247</v>
+        <v>0.1379899060258284</v>
       </c>
       <c r="J33" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K33" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02510719931730021</v>
+        <v>0.02317761310731781</v>
       </c>
       <c r="M33" t="n">
-        <v>4.821156558372333</v>
+        <v>4.834240190304274</v>
       </c>
       <c r="N33" t="n">
-        <v>43.87451392668167</v>
+        <v>43.94358485586952</v>
       </c>
       <c r="O33" t="n">
-        <v>6.623783958333912</v>
+        <v>6.628995765262603</v>
       </c>
       <c r="P33" t="n">
-        <v>377.8338757213588</v>
+        <v>377.8966381102784</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -33898,7 +34016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH261"/>
+  <dimension ref="A1:AH262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78541,6 +78659,178 @@
         </is>
       </c>
     </row>
+    <row r="262">
+      <c r="A262" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-30 22:06:00+00:00</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>-36.5887765869775,175.52483915391133</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>-36.58916036372396,175.5240973702233</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>-36.58967244414676,175.52349398194158</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>-36.59026625096092,175.52300952749164</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>-36.59095564518635,175.52279351940768</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>-36.59165136106527,175.52261487324816</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>-36.59236586979593,175.5226602665546</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>-36.59306717069515,175.5227875408251</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>-36.593741232959786,175.52303328581021</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>-36.594400274824054,175.52334992767203</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>-36.59504087341166,175.52371859081848</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>-36.5956639875481,175.524133891945</t>
+        </is>
+      </c>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>-36.59628747866372,175.5245520348088</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>-36.59686112153785,175.52507285275107</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>-36.59741561371119,175.52562918578215</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>-36.597966899946,175.5262052503623</t>
+        </is>
+      </c>
+      <c r="R262" t="inlineStr">
+        <is>
+          <t>-36.598504042855126,175.52680568111592</t>
+        </is>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>-36.5990179333548,175.52743049485792</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>-36.59950033677861,175.5280883925865</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>-36.59999576847681,175.52873715033334</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>-36.60048509893943,175.52939713076728</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>-36.600950429469066,175.5300736449308</t>
+        </is>
+      </c>
+      <c r="X262" t="inlineStr">
+        <is>
+          <t>-36.60138038857317,175.530777408983</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>-36.601794739676045,175.5315069411149</t>
+        </is>
+      </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t>-36.60220412404641,175.5322357014955</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>-36.60255995449123,175.53300383431295</t>
+        </is>
+      </c>
+      <c r="AB262" t="inlineStr">
+        <is>
+          <t>-36.602883735109664,175.5337969069521</t>
+        </is>
+      </c>
+      <c r="AC262" t="inlineStr">
+        <is>
+          <t>-36.603157155497655,175.53460237047435</t>
+        </is>
+      </c>
+      <c r="AD262" t="inlineStr">
+        <is>
+          <t>-36.60337208155412,175.53543128564445</t>
+        </is>
+      </c>
+      <c r="AE262" t="inlineStr">
+        <is>
+          <t>-36.60358051237272,175.5362829939915</t>
+        </is>
+      </c>
+      <c r="AF262" t="inlineStr">
+        <is>
+          <t>-36.60364453895662,175.5370630258254</t>
+        </is>
+      </c>
+      <c r="AG262" t="inlineStr">
+        <is>
+          <t>-36.60353835109835,175.5378627949952</t>
+        </is>
+      </c>
+      <c r="AH262" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH262"/>
+  <dimension ref="A1:AH263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28665,6 +28665,114 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B263" t="n">
+        <v>378.16</v>
+      </c>
+      <c r="C263" t="n">
+        <v>374.56</v>
+      </c>
+      <c r="D263" t="n">
+        <v>366.45</v>
+      </c>
+      <c r="E263" t="n">
+        <v>368.93</v>
+      </c>
+      <c r="F263" t="n">
+        <v>371.09</v>
+      </c>
+      <c r="G263" t="n">
+        <v>366.55</v>
+      </c>
+      <c r="H263" t="n">
+        <v>369.07</v>
+      </c>
+      <c r="I263" t="n">
+        <v>378.86</v>
+      </c>
+      <c r="J263" t="n">
+        <v>379.67</v>
+      </c>
+      <c r="K263" t="n">
+        <v>381.81</v>
+      </c>
+      <c r="L263" t="n">
+        <v>383.11</v>
+      </c>
+      <c r="M263" t="n">
+        <v>385.59</v>
+      </c>
+      <c r="N263" t="n">
+        <v>380.16</v>
+      </c>
+      <c r="O263" t="n">
+        <v>379.9</v>
+      </c>
+      <c r="P263" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>370.38</v>
+      </c>
+      <c r="R263" t="n">
+        <v>371.79</v>
+      </c>
+      <c r="S263" t="n">
+        <v>373.29</v>
+      </c>
+      <c r="T263" t="n">
+        <v>375.44</v>
+      </c>
+      <c r="U263" t="n">
+        <v>374.8</v>
+      </c>
+      <c r="V263" t="n">
+        <v>374.61</v>
+      </c>
+      <c r="W263" t="n">
+        <v>378.79</v>
+      </c>
+      <c r="X263" t="n">
+        <v>380.43</v>
+      </c>
+      <c r="Y263" t="n">
+        <v>379.7</v>
+      </c>
+      <c r="Z263" t="n">
+        <v>379.09</v>
+      </c>
+      <c r="AA263" t="n">
+        <v>379.07</v>
+      </c>
+      <c r="AB263" t="n">
+        <v>380.01</v>
+      </c>
+      <c r="AC263" t="n">
+        <v>385.48</v>
+      </c>
+      <c r="AD263" t="n">
+        <v>385.22</v>
+      </c>
+      <c r="AE263" t="n">
+        <v>381.3</v>
+      </c>
+      <c r="AF263" t="n">
+        <v>393.81</v>
+      </c>
+      <c r="AG263" t="n">
+        <v>376.46</v>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28676,7 +28784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B268"/>
+  <dimension ref="A1:B269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31359,6 +31467,16 @@
       </c>
       <c r="B268" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>0.55</v>
       </c>
     </row>
   </sheetData>
@@ -31527,28 +31645,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1869594787275971</v>
+        <v>-0.1849196044246146</v>
       </c>
       <c r="J2" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K2" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03725020944161184</v>
+        <v>0.03674463913852843</v>
       </c>
       <c r="M2" t="n">
-        <v>5.606485407922931</v>
+        <v>5.593748866993093</v>
       </c>
       <c r="N2" t="n">
-        <v>48.09718138546668</v>
+        <v>47.93670560993132</v>
       </c>
       <c r="O2" t="n">
-        <v>6.935213146361594</v>
+        <v>6.923633844299633</v>
       </c>
       <c r="P2" t="n">
-        <v>380.4725631008428</v>
+        <v>380.4505052695569</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31605,28 +31723,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2648794250780183</v>
+        <v>-0.2594570649548752</v>
       </c>
       <c r="J3" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K3" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0720127059908281</v>
+        <v>0.06957491502292013</v>
       </c>
       <c r="M3" t="n">
-        <v>5.48771381488867</v>
+        <v>5.495113702731342</v>
       </c>
       <c r="N3" t="n">
-        <v>48.82305240839349</v>
+        <v>48.82622971106987</v>
       </c>
       <c r="O3" t="n">
-        <v>6.987349455150607</v>
+        <v>6.987576812534505</v>
       </c>
       <c r="P3" t="n">
-        <v>374.4814859185254</v>
+        <v>374.423414389216</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31683,28 +31801,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3971887357314901</v>
+        <v>-0.3926176467843513</v>
       </c>
       <c r="J4" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K4" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1063578146002186</v>
+        <v>0.1047766043063164</v>
       </c>
       <c r="M4" t="n">
-        <v>6.514851212918247</v>
+        <v>6.514500579548252</v>
       </c>
       <c r="N4" t="n">
-        <v>70.57128725343665</v>
+        <v>70.43062793189259</v>
       </c>
       <c r="O4" t="n">
-        <v>8.400671833456933</v>
+        <v>8.39229574859541</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0648231831938</v>
+        <v>371.0153944960232</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31761,28 +31879,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6293691537959664</v>
+        <v>-0.6287398720138437</v>
       </c>
       <c r="J5" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K5" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1642345353185292</v>
+        <v>0.1650995684655997</v>
       </c>
       <c r="M5" t="n">
-        <v>8.010066954288771</v>
+        <v>7.982397941694343</v>
       </c>
       <c r="N5" t="n">
-        <v>106.7620962246082</v>
+        <v>106.3475803260637</v>
       </c>
       <c r="O5" t="n">
-        <v>10.33257452064142</v>
+        <v>10.31249631883879</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7873189242916</v>
+        <v>384.7804829531372</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31839,28 +31957,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5850277533009046</v>
+        <v>-0.5827158091789821</v>
       </c>
       <c r="J6" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K6" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1121066817367934</v>
+        <v>0.1121210824559379</v>
       </c>
       <c r="M6" t="n">
-        <v>9.368704359150225</v>
+        <v>9.345006425974656</v>
       </c>
       <c r="N6" t="n">
-        <v>144.7421199422733</v>
+        <v>144.2154893647006</v>
       </c>
       <c r="O6" t="n">
-        <v>12.03088192703566</v>
+        <v>12.00897536697867</v>
       </c>
       <c r="P6" t="n">
-        <v>383.5851251189397</v>
+        <v>383.5601998350148</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -31917,28 +32035,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6801260551620667</v>
+        <v>-0.6792771513391176</v>
       </c>
       <c r="J7" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K7" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05130791483035513</v>
+        <v>0.05159110008288981</v>
       </c>
       <c r="M7" t="n">
-        <v>16.99701035167684</v>
+        <v>16.93374888515555</v>
       </c>
       <c r="N7" t="n">
-        <v>453.7008672968728</v>
+        <v>451.9331990505859</v>
       </c>
       <c r="O7" t="n">
-        <v>21.30025509933796</v>
+        <v>21.25872054124109</v>
       </c>
       <c r="P7" t="n">
-        <v>383.4681561039909</v>
+        <v>383.4589437583608</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -31999,28 +32117,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4646503843219361</v>
+        <v>0.4590138894964891</v>
       </c>
       <c r="J8" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K8" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03115922519878711</v>
+        <v>0.03065905184800921</v>
       </c>
       <c r="M8" t="n">
-        <v>14.96886974580191</v>
+        <v>14.93421731460263</v>
       </c>
       <c r="N8" t="n">
-        <v>359.4972830796773</v>
+        <v>358.2817479491349</v>
       </c>
       <c r="O8" t="n">
-        <v>18.96041357881408</v>
+        <v>18.92833188501129</v>
       </c>
       <c r="P8" t="n">
-        <v>364.0239066021311</v>
+        <v>364.0848919931991</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32081,28 +32199,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6444814138947415</v>
+        <v>0.638125631370958</v>
       </c>
       <c r="J9" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K9" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1201857176776623</v>
+        <v>0.1187951816666171</v>
       </c>
       <c r="M9" t="n">
-        <v>10.19003886899285</v>
+        <v>10.17826165885564</v>
       </c>
       <c r="N9" t="n">
-        <v>166.4090057136357</v>
+        <v>166.0278004262487</v>
       </c>
       <c r="O9" t="n">
-        <v>12.89996146171126</v>
+        <v>12.88517754733122</v>
       </c>
       <c r="P9" t="n">
-        <v>370.1384634875504</v>
+        <v>370.2060607891692</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32163,28 +32281,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4230846596414497</v>
+        <v>0.4196766778098315</v>
       </c>
       <c r="J10" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K10" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L10" t="n">
-        <v>0.109195909427798</v>
+        <v>0.1083318369168378</v>
       </c>
       <c r="M10" t="n">
-        <v>7.029689770009086</v>
+        <v>7.018584126089923</v>
       </c>
       <c r="N10" t="n">
-        <v>79.66537856506058</v>
+        <v>79.43597240159943</v>
       </c>
       <c r="O10" t="n">
-        <v>8.92554640148493</v>
+        <v>8.912686037418766</v>
       </c>
       <c r="P10" t="n">
-        <v>372.9663069369802</v>
+        <v>373.0024804294713</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32241,28 +32359,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3708437169321578</v>
+        <v>0.3693142324695052</v>
       </c>
       <c r="J11" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K11" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1126982981602288</v>
+        <v>0.1126761485849017</v>
       </c>
       <c r="M11" t="n">
-        <v>6.1439241827499</v>
+        <v>6.12668146132525</v>
       </c>
       <c r="N11" t="n">
-        <v>57.79407305960007</v>
+        <v>57.5851031339282</v>
       </c>
       <c r="O11" t="n">
-        <v>7.602241318164011</v>
+        <v>7.58848490371617</v>
       </c>
       <c r="P11" t="n">
-        <v>373.9766456542228</v>
+        <v>373.9931381971382</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32319,28 +32437,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3984632161164965</v>
+        <v>0.3992170666555876</v>
       </c>
       <c r="J12" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K12" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1332691733117016</v>
+        <v>0.13466360738006</v>
       </c>
       <c r="M12" t="n">
-        <v>6.036681480705899</v>
+        <v>6.01734882301764</v>
       </c>
       <c r="N12" t="n">
-        <v>55.11610346991776</v>
+        <v>54.90612836317838</v>
       </c>
       <c r="O12" t="n">
-        <v>7.4240220547839</v>
+        <v>7.409866959883853</v>
       </c>
       <c r="P12" t="n">
-        <v>371.5817251385138</v>
+        <v>371.5735963129707</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32397,28 +32515,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2898024515677483</v>
+        <v>0.2916368746437587</v>
       </c>
       <c r="J13" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K13" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1001897121080753</v>
+        <v>0.102042588201167</v>
       </c>
       <c r="M13" t="n">
-        <v>5.071724194456687</v>
+        <v>5.061833908897615</v>
       </c>
       <c r="N13" t="n">
-        <v>40.26052474702025</v>
+        <v>40.12610847233999</v>
       </c>
       <c r="O13" t="n">
-        <v>6.345118182273696</v>
+        <v>6.334517224883045</v>
       </c>
       <c r="P13" t="n">
-        <v>375.5423392080567</v>
+        <v>375.5225584897527</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32475,28 +32593,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1367570795996907</v>
+        <v>0.1355854532451597</v>
       </c>
       <c r="J14" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K14" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03449879715759241</v>
+        <v>0.03419258887107846</v>
       </c>
       <c r="M14" t="n">
-        <v>4.292381344335165</v>
+        <v>4.28024183390187</v>
       </c>
       <c r="N14" t="n">
-        <v>28.10915521569409</v>
+        <v>28.00951726609275</v>
       </c>
       <c r="O14" t="n">
-        <v>5.301806787850166</v>
+        <v>5.292401842839671</v>
       </c>
       <c r="P14" t="n">
-        <v>378.0620672962912</v>
+        <v>378.0746367548937</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32553,28 +32671,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2890798939710978</v>
+        <v>0.2877777404477521</v>
       </c>
       <c r="J15" t="n">
+        <v>262</v>
+      </c>
+      <c r="K15" t="n">
         <v>261</v>
       </c>
-      <c r="K15" t="n">
-        <v>260</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1691120471416265</v>
+        <v>0.1689276830864823</v>
       </c>
       <c r="M15" t="n">
-        <v>3.787905632181781</v>
+        <v>3.778285538620856</v>
       </c>
       <c r="N15" t="n">
-        <v>22.52699620301343</v>
+        <v>22.45200516577562</v>
       </c>
       <c r="O15" t="n">
-        <v>4.746261286846041</v>
+        <v>4.738354689739428</v>
       </c>
       <c r="P15" t="n">
-        <v>373.9709021992841</v>
+        <v>373.984655283687</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32631,28 +32749,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.179192792558631</v>
+        <v>0.176821488167172</v>
       </c>
       <c r="J16" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K16" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08947327110670644</v>
+        <v>0.08781689686202121</v>
       </c>
       <c r="M16" t="n">
-        <v>3.541587398262191</v>
+        <v>3.538454966595282</v>
       </c>
       <c r="N16" t="n">
-        <v>17.89346340509092</v>
+        <v>17.86256669291658</v>
       </c>
       <c r="O16" t="n">
-        <v>4.230066595822213</v>
+        <v>4.226412981822361</v>
       </c>
       <c r="P16" t="n">
-        <v>374.6557447738422</v>
+        <v>374.6807878599446</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32709,28 +32827,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2189310497837067</v>
+        <v>0.2131422493082996</v>
       </c>
       <c r="J17" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K17" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1212920779648021</v>
+        <v>0.1153412106251329</v>
       </c>
       <c r="M17" t="n">
-        <v>3.489170443881513</v>
+        <v>3.50387429266907</v>
       </c>
       <c r="N17" t="n">
-        <v>19.01431895716643</v>
+        <v>19.1646205285362</v>
       </c>
       <c r="O17" t="n">
-        <v>4.360541131232043</v>
+        <v>4.377741487175345</v>
       </c>
       <c r="P17" t="n">
-        <v>372.2703674262361</v>
+        <v>372.3315023143837</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32787,28 +32905,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1596512425625559</v>
+        <v>0.154675371703428</v>
       </c>
       <c r="J18" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K18" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0623677291501844</v>
+        <v>0.05878706030749214</v>
       </c>
       <c r="M18" t="n">
-        <v>3.684356040497691</v>
+        <v>3.688072693880292</v>
       </c>
       <c r="N18" t="n">
-        <v>20.98317347379895</v>
+        <v>21.0677582520384</v>
       </c>
       <c r="O18" t="n">
-        <v>4.580739402519963</v>
+        <v>4.589962772402234</v>
       </c>
       <c r="P18" t="n">
-        <v>374.1738546856786</v>
+        <v>374.2264043131363</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32865,28 +32983,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1647031596905636</v>
+        <v>0.1589975891910399</v>
       </c>
       <c r="J19" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K19" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L19" t="n">
-        <v>0.06196053361432097</v>
+        <v>0.05791121475909033</v>
       </c>
       <c r="M19" t="n">
-        <v>3.740070028806902</v>
+        <v>3.740223978110565</v>
       </c>
       <c r="N19" t="n">
-        <v>22.48867009924877</v>
+        <v>22.6193479664145</v>
       </c>
       <c r="O19" t="n">
-        <v>4.742222063468641</v>
+        <v>4.755980231920072</v>
       </c>
       <c r="P19" t="n">
-        <v>376.5091491190851</v>
+        <v>376.5694050245682</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -32943,28 +33061,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1289851583176413</v>
+        <v>0.124801107923103</v>
       </c>
       <c r="J20" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K20" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L20" t="n">
-        <v>0.04047302565782407</v>
+        <v>0.03809187270322778</v>
       </c>
       <c r="M20" t="n">
-        <v>3.677142518450611</v>
+        <v>3.677644548674943</v>
       </c>
       <c r="N20" t="n">
-        <v>21.5985675112905</v>
+        <v>21.63256390637872</v>
       </c>
       <c r="O20" t="n">
-        <v>4.647425901646039</v>
+        <v>4.651082014583136</v>
       </c>
       <c r="P20" t="n">
-        <v>377.5860036305029</v>
+        <v>377.6301909287109</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33021,28 +33139,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1738730049091698</v>
+        <v>0.1705561537164514</v>
       </c>
       <c r="J21" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K21" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06986675823333588</v>
+        <v>0.06771374860057588</v>
       </c>
       <c r="M21" t="n">
-        <v>3.675895702246787</v>
+        <v>3.677110657029868</v>
       </c>
       <c r="N21" t="n">
-        <v>22.03904860951248</v>
+        <v>22.02810072925021</v>
       </c>
       <c r="O21" t="n">
-        <v>4.694576510135124</v>
+        <v>4.693410351679279</v>
       </c>
       <c r="P21" t="n">
-        <v>374.6006744655838</v>
+        <v>374.6357033679497</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33099,28 +33217,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2303236292828086</v>
+        <v>0.2264067286349167</v>
       </c>
       <c r="J22" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K22" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1017466939196349</v>
+        <v>0.09903250848646905</v>
       </c>
       <c r="M22" t="n">
-        <v>4.099006271683802</v>
+        <v>4.102445428586055</v>
       </c>
       <c r="N22" t="n">
-        <v>25.64539889584213</v>
+        <v>25.64955556614732</v>
       </c>
       <c r="O22" t="n">
-        <v>5.064128641320452</v>
+        <v>5.064539028001198</v>
       </c>
       <c r="P22" t="n">
-        <v>373.7127249243156</v>
+        <v>373.754090883293</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33177,28 +33295,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2006729397518565</v>
+        <v>0.1982637995296845</v>
       </c>
       <c r="J23" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K23" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08473881986431364</v>
+        <v>0.08338786757335337</v>
       </c>
       <c r="M23" t="n">
-        <v>3.998315644775991</v>
+        <v>3.995243306719424</v>
       </c>
       <c r="N23" t="n">
-        <v>23.81739214754613</v>
+        <v>23.76508799465064</v>
       </c>
       <c r="O23" t="n">
-        <v>4.880306562865301</v>
+        <v>4.874944922217137</v>
       </c>
       <c r="P23" t="n">
-        <v>376.6721874585469</v>
+        <v>376.6976301247159</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33255,28 +33373,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1849908104675219</v>
+        <v>0.1842442592486468</v>
       </c>
       <c r="J24" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K24" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06347628798607874</v>
+        <v>0.06347708883157333</v>
       </c>
       <c r="M24" t="n">
-        <v>4.213387093794736</v>
+        <v>4.200914756330376</v>
       </c>
       <c r="N24" t="n">
-        <v>27.64785966823055</v>
+        <v>27.54604032775282</v>
       </c>
       <c r="O24" t="n">
-        <v>5.258123207783415</v>
+        <v>5.248432178065448</v>
       </c>
       <c r="P24" t="n">
-        <v>376.5261367969695</v>
+        <v>376.5340210426704</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33333,28 +33451,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1775251175849696</v>
+        <v>0.1764871667083538</v>
       </c>
       <c r="J25" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K25" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06111977709075189</v>
+        <v>0.06090416402527465</v>
       </c>
       <c r="M25" t="n">
-        <v>4.08466090545524</v>
+        <v>4.073759252650709</v>
       </c>
       <c r="N25" t="n">
-        <v>26.50952813946149</v>
+        <v>26.41551210060922</v>
       </c>
       <c r="O25" t="n">
-        <v>5.14874044203643</v>
+        <v>5.139602329033757</v>
       </c>
       <c r="P25" t="n">
-        <v>376.3741563088534</v>
+        <v>376.3851179944417</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -33411,28 +33529,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1512089577395586</v>
+        <v>0.1471742402396861</v>
       </c>
       <c r="J26" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K26" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05302005812297261</v>
+        <v>0.05053120705761305</v>
       </c>
       <c r="M26" t="n">
-        <v>3.74713799674202</v>
+        <v>3.75129956371273</v>
       </c>
       <c r="N26" t="n">
-        <v>22.36194478430541</v>
+        <v>22.38486457836223</v>
       </c>
       <c r="O26" t="n">
-        <v>4.728841801573131</v>
+        <v>4.731264585537595</v>
       </c>
       <c r="P26" t="n">
-        <v>380.4475194634881</v>
+        <v>380.4901296733424</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -33489,28 +33607,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1139127836969717</v>
+        <v>0.1102870570211196</v>
       </c>
       <c r="J27" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K27" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02883345362821843</v>
+        <v>0.02719687473389976</v>
       </c>
       <c r="M27" t="n">
-        <v>3.935114390475948</v>
+        <v>3.936064021243697</v>
       </c>
       <c r="N27" t="n">
-        <v>23.93293323639565</v>
+        <v>23.92901906994764</v>
       </c>
       <c r="O27" t="n">
-        <v>4.892129723995026</v>
+        <v>4.891729660349971</v>
       </c>
       <c r="P27" t="n">
-        <v>380.8719835857915</v>
+        <v>380.9102744883236</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -33567,28 +33685,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1651854621641731</v>
+        <v>0.159951189578786</v>
       </c>
       <c r="J28" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K28" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04690085452644199</v>
+        <v>0.04419873168627053</v>
       </c>
       <c r="M28" t="n">
-        <v>4.524352498650936</v>
+        <v>4.526842133187027</v>
       </c>
       <c r="N28" t="n">
-        <v>30.36371597989458</v>
+        <v>30.43004453138933</v>
       </c>
       <c r="O28" t="n">
-        <v>5.510328119077355</v>
+        <v>5.5163434022357</v>
       </c>
       <c r="P28" t="n">
-        <v>382.5871408065398</v>
+        <v>382.6424193863425</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -33645,28 +33763,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2019932208379856</v>
+        <v>0.1971409509959723</v>
       </c>
       <c r="J29" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K29" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L29" t="n">
-        <v>0.07519314031345825</v>
+        <v>0.07204957602752937</v>
       </c>
       <c r="M29" t="n">
-        <v>4.328709658861087</v>
+        <v>4.334983061338107</v>
       </c>
       <c r="N29" t="n">
-        <v>27.47896420243538</v>
+        <v>27.53067650314107</v>
       </c>
       <c r="O29" t="n">
-        <v>5.24203817254657</v>
+        <v>5.246968315431404</v>
       </c>
       <c r="P29" t="n">
-        <v>386.5801375727154</v>
+        <v>386.6313818633614</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -33723,28 +33841,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2289186363171574</v>
+        <v>0.224936509670782</v>
       </c>
       <c r="J30" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K30" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1287498501724427</v>
+        <v>0.1251700454385276</v>
       </c>
       <c r="M30" t="n">
-        <v>3.512954789727684</v>
+        <v>3.514955573078324</v>
       </c>
       <c r="N30" t="n">
-        <v>19.41835265435088</v>
+        <v>19.44970340086954</v>
       </c>
       <c r="O30" t="n">
-        <v>4.406625994380608</v>
+        <v>4.410181787735007</v>
       </c>
       <c r="P30" t="n">
-        <v>384.4465526886628</v>
+        <v>384.4886074922702</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -33801,28 +33919,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1736725671971746</v>
+        <v>0.1686541223710787</v>
       </c>
       <c r="J31" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K31" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L31" t="n">
-        <v>0.07050880414637306</v>
+        <v>0.06679475729033946</v>
       </c>
       <c r="M31" t="n">
-        <v>3.809187731406042</v>
+        <v>3.816202035353335</v>
       </c>
       <c r="N31" t="n">
-        <v>21.77300286913616</v>
+        <v>21.85740300230584</v>
       </c>
       <c r="O31" t="n">
-        <v>4.666155041266435</v>
+        <v>4.675190156807083</v>
       </c>
       <c r="P31" t="n">
-        <v>383.3641031109622</v>
+        <v>383.4171023574247</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -33879,28 +33997,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2124902030946642</v>
+        <v>0.2072416111307513</v>
       </c>
       <c r="J32" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K32" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L32" t="n">
-        <v>0.09327373840660025</v>
+        <v>0.08917820907377461</v>
       </c>
       <c r="M32" t="n">
-        <v>3.808351906988444</v>
+        <v>3.817746676911829</v>
       </c>
       <c r="N32" t="n">
-        <v>24.03524670977357</v>
+        <v>24.12672808819072</v>
       </c>
       <c r="O32" t="n">
-        <v>4.90257551800822</v>
+        <v>4.911896587693059</v>
       </c>
       <c r="P32" t="n">
-        <v>395.1585046888048</v>
+        <v>395.2139344939966</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -33957,28 +34075,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1379899060258284</v>
+        <v>0.1341541744861846</v>
       </c>
       <c r="J33" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K33" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02317761310731781</v>
+        <v>0.02206399965852424</v>
       </c>
       <c r="M33" t="n">
-        <v>4.834240190304274</v>
+        <v>4.836153498841488</v>
       </c>
       <c r="N33" t="n">
-        <v>43.94358485586952</v>
+        <v>43.87371583952162</v>
       </c>
       <c r="O33" t="n">
-        <v>6.628995765262603</v>
+        <v>6.623723714008731</v>
       </c>
       <c r="P33" t="n">
-        <v>377.8966381102784</v>
+        <v>377.9371468511888</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34016,7 +34134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH262"/>
+  <dimension ref="A1:AH263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -78831,6 +78949,178 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>-36.58879168704214,175.5248532895287</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>-36.589176758555375,175.52411780299258</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>-36.589683086095754,175.52351283729368</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>-36.59027567038166,175.52303685391612</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>-36.59096428620623,175.52284549505075</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>-36.59165166940847,175.52262111813369</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>-36.59236483671309,175.52268302256041</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>-36.59306212447239,175.52282410240062</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-36.593734107413994,175.52306119284873</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>-36.59439885042245,175.5233542751026</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>-36.59503671404471,175.52372887818862</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr">
+        <is>
+          <t>-36.595655161669285,175.52415234174106</t>
+        </is>
+      </c>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>-36.59627637015503,175.52457144077937</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>-36.59684792257618,175.52509266338507</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>-36.59740726128804,175.52564030372938</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>-36.59796671367135,175.52620549324274</t>
+        </is>
+      </c>
+      <c r="R263" t="inlineStr">
+        <is>
+          <t>-36.598494229715655,175.52681862354834</t>
+        </is>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>-36.59901361198421,175.52743588058715</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>-36.59950325057951,175.52808505919157</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>-36.599993139774135,175.52874004185557</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>-36.60048172879505,175.52940083784952</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>-36.60093661854068,175.5300876476172</t>
+        </is>
+      </c>
+      <c r="X263" t="inlineStr">
+        <is>
+          <t>-36.60136038512948,175.53079515803162</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>-36.601778568857696,175.53152056799442</t>
+        </is>
+      </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t>-36.60219399550323,175.53224343102318</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>-36.60254965264975,175.533010744965</t>
+        </is>
+      </c>
+      <c r="AB263" t="inlineStr">
+        <is>
+          <t>-36.602885836911724,175.53379562437226</t>
+        </is>
+      </c>
+      <c r="AC263" t="inlineStr">
+        <is>
+          <t>-36.60314451888619,175.5346083113777</t>
+        </is>
+      </c>
+      <c r="AD263" t="inlineStr">
+        <is>
+          <t>-36.60336129999976,175.53543491477396</t>
+        </is>
+      </c>
+      <c r="AE263" t="inlineStr">
+        <is>
+          <t>-36.60357358157512,175.5362850018978</t>
+        </is>
+      </c>
+      <c r="AF263" t="inlineStr">
+        <is>
+          <t>-36.6036310953083,175.5370613181414</t>
+        </is>
+      </c>
+      <c r="AG263" t="inlineStr">
+        <is>
+          <t>-36.60351579382767,175.53785008587323</t>
+        </is>
+      </c>
+      <c r="AH263" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH263"/>
+  <dimension ref="A1:AH264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28773,6 +28773,114 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B264" t="n">
+        <v>377.66</v>
+      </c>
+      <c r="C264" t="n">
+        <v>375</v>
+      </c>
+      <c r="D264" t="n">
+        <v>366.18</v>
+      </c>
+      <c r="E264" t="n">
+        <v>370.06</v>
+      </c>
+      <c r="F264" t="n">
+        <v>375.13</v>
+      </c>
+      <c r="G264" t="n">
+        <v>370.07</v>
+      </c>
+      <c r="H264" t="n">
+        <v>370.9</v>
+      </c>
+      <c r="I264" t="n">
+        <v>383.27</v>
+      </c>
+      <c r="J264" t="n">
+        <v>380.06</v>
+      </c>
+      <c r="K264" t="n">
+        <v>381.89</v>
+      </c>
+      <c r="L264" t="n">
+        <v>382.36</v>
+      </c>
+      <c r="M264" t="n">
+        <v>385.22</v>
+      </c>
+      <c r="N264" t="n">
+        <v>380.28</v>
+      </c>
+      <c r="O264" t="n">
+        <v>379.53</v>
+      </c>
+      <c r="P264" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>371.17</v>
+      </c>
+      <c r="R264" t="n">
+        <v>371.77</v>
+      </c>
+      <c r="S264" t="n">
+        <v>373.6</v>
+      </c>
+      <c r="T264" t="n">
+        <v>375.11</v>
+      </c>
+      <c r="U264" t="n">
+        <v>373.45</v>
+      </c>
+      <c r="V264" t="n">
+        <v>375.35</v>
+      </c>
+      <c r="W264" t="n">
+        <v>378.82</v>
+      </c>
+      <c r="X264" t="n">
+        <v>380.24</v>
+      </c>
+      <c r="Y264" t="n">
+        <v>379.23</v>
+      </c>
+      <c r="Z264" t="n">
+        <v>380.06</v>
+      </c>
+      <c r="AA264" t="n">
+        <v>379.81</v>
+      </c>
+      <c r="AB264" t="n">
+        <v>380.09</v>
+      </c>
+      <c r="AC264" t="n">
+        <v>384.74</v>
+      </c>
+      <c r="AD264" t="n">
+        <v>383.31</v>
+      </c>
+      <c r="AE264" t="n">
+        <v>381.18</v>
+      </c>
+      <c r="AF264" t="n">
+        <v>394.49</v>
+      </c>
+      <c r="AG264" t="n">
+        <v>377.43</v>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28784,7 +28892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B269"/>
+  <dimension ref="A1:B270"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31477,6 +31585,16 @@
       </c>
       <c r="B269" t="n">
         <v>0.55</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>0.39</v>
       </c>
     </row>
   </sheetData>
@@ -31645,28 +31763,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1849196044246146</v>
+        <v>-0.1832889809826659</v>
       </c>
       <c r="J2" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K2" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03674463913852843</v>
+        <v>0.03639943432694237</v>
       </c>
       <c r="M2" t="n">
-        <v>5.593748866993093</v>
+        <v>5.579487417787073</v>
       </c>
       <c r="N2" t="n">
-        <v>47.93670560993132</v>
+        <v>47.76808819086664</v>
       </c>
       <c r="O2" t="n">
-        <v>6.923633844299633</v>
+        <v>6.911446172174578</v>
       </c>
       <c r="P2" t="n">
-        <v>380.4505052695569</v>
+        <v>380.4328225245234</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31723,28 +31841,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2594570649548752</v>
+        <v>-0.253778395723105</v>
       </c>
       <c r="J3" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K3" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06957491502292013</v>
+        <v>0.06700458842823964</v>
       </c>
       <c r="M3" t="n">
-        <v>5.495113702731342</v>
+        <v>5.504132738916353</v>
       </c>
       <c r="N3" t="n">
-        <v>48.82622971106987</v>
+        <v>48.85046620274551</v>
       </c>
       <c r="O3" t="n">
-        <v>6.987576812534505</v>
+        <v>6.989310853206167</v>
       </c>
       <c r="P3" t="n">
-        <v>374.423414389216</v>
+        <v>374.3624223206785</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31801,28 +31919,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3926176467843513</v>
+        <v>-0.3883195878965702</v>
       </c>
       <c r="J4" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K4" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1047766043063164</v>
+        <v>0.1033372872315323</v>
       </c>
       <c r="M4" t="n">
-        <v>6.514500579548252</v>
+        <v>6.513236688893291</v>
       </c>
       <c r="N4" t="n">
-        <v>70.43062793189259</v>
+        <v>70.27702763285053</v>
       </c>
       <c r="O4" t="n">
-        <v>8.39229574859541</v>
+        <v>8.383139485470258</v>
       </c>
       <c r="P4" t="n">
-        <v>371.0153944960232</v>
+        <v>370.9687856484523</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31879,28 +31997,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6287398720138437</v>
+        <v>-0.6272120794068381</v>
       </c>
       <c r="J5" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K5" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1650995684655997</v>
+        <v>0.165551470917314</v>
       </c>
       <c r="M5" t="n">
-        <v>7.982397941694343</v>
+        <v>7.960041122347571</v>
       </c>
       <c r="N5" t="n">
-        <v>106.3475803260637</v>
+        <v>105.9487729027918</v>
       </c>
       <c r="O5" t="n">
-        <v>10.31249631883879</v>
+        <v>10.29314203257644</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7804829531372</v>
+        <v>384.7638390801141</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -31957,28 +32075,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5827158091789821</v>
+        <v>-0.5773179821578374</v>
       </c>
       <c r="J6" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K6" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1121210824559379</v>
+        <v>0.1109659527961968</v>
       </c>
       <c r="M6" t="n">
-        <v>9.345006425974656</v>
+        <v>9.338088762214507</v>
       </c>
       <c r="N6" t="n">
-        <v>144.2154893647006</v>
+        <v>143.8476510622471</v>
       </c>
       <c r="O6" t="n">
-        <v>12.00897536697867</v>
+        <v>11.99365044772637</v>
       </c>
       <c r="P6" t="n">
-        <v>383.5601998350148</v>
+        <v>383.5018394657611</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32035,28 +32153,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6792771513391176</v>
+        <v>-0.6756873118093527</v>
       </c>
       <c r="J7" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K7" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05159110008288981</v>
+        <v>0.05146880447223434</v>
       </c>
       <c r="M7" t="n">
-        <v>16.93374888515555</v>
+        <v>16.88095883365991</v>
       </c>
       <c r="N7" t="n">
-        <v>451.9331990505859</v>
+        <v>450.2576514601075</v>
       </c>
       <c r="O7" t="n">
-        <v>21.25872054124109</v>
+        <v>21.21927546972581</v>
       </c>
       <c r="P7" t="n">
-        <v>383.4589437583608</v>
+        <v>383.4198755648755</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32117,28 +32235,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4590138894964891</v>
+        <v>0.4548696333061872</v>
       </c>
       <c r="J8" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K8" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03065905184800921</v>
+        <v>0.03035737469909239</v>
       </c>
       <c r="M8" t="n">
-        <v>14.93421731460263</v>
+        <v>14.89324646168774</v>
       </c>
       <c r="N8" t="n">
-        <v>358.2817479491349</v>
+        <v>356.9831344178612</v>
       </c>
       <c r="O8" t="n">
-        <v>18.92833188501129</v>
+        <v>18.89399731178824</v>
       </c>
       <c r="P8" t="n">
-        <v>364.0848919931991</v>
+        <v>364.1298619238306</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32199,28 +32317,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.638125631370958</v>
+        <v>0.6351904596725184</v>
       </c>
       <c r="J9" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K9" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1187951816666171</v>
+        <v>0.1186512505227907</v>
       </c>
       <c r="M9" t="n">
-        <v>10.17826165885564</v>
+        <v>10.15145351613835</v>
       </c>
       <c r="N9" t="n">
-        <v>166.0278004262487</v>
+        <v>165.439577781397</v>
       </c>
       <c r="O9" t="n">
-        <v>12.88517754733122</v>
+        <v>12.8623317396729</v>
       </c>
       <c r="P9" t="n">
-        <v>370.2060607891692</v>
+        <v>370.2373697474468</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32281,28 +32399,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4196766778098315</v>
+        <v>0.4166024116638564</v>
       </c>
       <c r="J10" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K10" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1083318369168378</v>
+        <v>0.1076284801779133</v>
       </c>
       <c r="M10" t="n">
-        <v>7.018584126089923</v>
+        <v>7.006012500083153</v>
       </c>
       <c r="N10" t="n">
-        <v>79.43597240159943</v>
+        <v>79.19478966577257</v>
       </c>
       <c r="O10" t="n">
-        <v>8.912686037418766</v>
+        <v>8.899145445815153</v>
       </c>
       <c r="P10" t="n">
-        <v>373.0024804294713</v>
+        <v>373.035206318189</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32359,28 +32477,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3693142324695052</v>
+        <v>0.36784868847747</v>
       </c>
       <c r="J11" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K11" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1126761485849017</v>
+        <v>0.1126840613000434</v>
       </c>
       <c r="M11" t="n">
-        <v>6.12668146132525</v>
+        <v>6.109297630208819</v>
       </c>
       <c r="N11" t="n">
-        <v>57.5851031339282</v>
+        <v>57.37668742534845</v>
       </c>
       <c r="O11" t="n">
-        <v>7.58848490371617</v>
+        <v>7.574740089623435</v>
       </c>
       <c r="P11" t="n">
-        <v>373.9931381971382</v>
+        <v>374.0089862913412</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32437,28 +32555,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3992170666555876</v>
+        <v>0.3993579985380245</v>
       </c>
       <c r="J12" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K12" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L12" t="n">
-        <v>0.13466360738006</v>
+        <v>0.1357132092211084</v>
       </c>
       <c r="M12" t="n">
-        <v>6.01734882301764</v>
+        <v>5.994873950038083</v>
       </c>
       <c r="N12" t="n">
-        <v>54.90612836317838</v>
+        <v>54.69426431924255</v>
       </c>
       <c r="O12" t="n">
-        <v>7.409866959883853</v>
+        <v>7.395557066187952</v>
       </c>
       <c r="P12" t="n">
-        <v>371.5735963129707</v>
+        <v>371.5720723043015</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32515,28 +32633,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2916368746437587</v>
+        <v>0.2931383948091532</v>
       </c>
       <c r="J13" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K13" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L13" t="n">
-        <v>0.102042588201167</v>
+        <v>0.1037204583554792</v>
       </c>
       <c r="M13" t="n">
-        <v>5.061833908897615</v>
+        <v>5.050209026103771</v>
       </c>
       <c r="N13" t="n">
-        <v>40.12610847233999</v>
+        <v>39.98579384378687</v>
       </c>
       <c r="O13" t="n">
-        <v>6.334517224883045</v>
+        <v>6.323432125340389</v>
       </c>
       <c r="P13" t="n">
-        <v>375.5225584897527</v>
+        <v>375.5063213565392</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32593,28 +32711,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1355854532451597</v>
+        <v>0.1345234712462887</v>
       </c>
       <c r="J14" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K14" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03419258887107846</v>
+        <v>0.03393826987120618</v>
       </c>
       <c r="M14" t="n">
-        <v>4.28024183390187</v>
+        <v>4.267751112060046</v>
       </c>
       <c r="N14" t="n">
-        <v>28.00951726609275</v>
+        <v>27.90915379392053</v>
       </c>
       <c r="O14" t="n">
-        <v>5.292401842839671</v>
+        <v>5.282911488367048</v>
       </c>
       <c r="P14" t="n">
-        <v>378.0746367548937</v>
+        <v>378.0860624750952</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32671,28 +32789,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2877777404477521</v>
+        <v>0.2862089764703989</v>
       </c>
       <c r="J15" t="n">
+        <v>263</v>
+      </c>
+      <c r="K15" t="n">
         <v>262</v>
       </c>
-      <c r="K15" t="n">
-        <v>261</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1689276830864823</v>
+        <v>0.1684393039803077</v>
       </c>
       <c r="M15" t="n">
-        <v>3.778285538620856</v>
+        <v>3.769690940868807</v>
       </c>
       <c r="N15" t="n">
-        <v>22.45200516577562</v>
+        <v>22.38287393902614</v>
       </c>
       <c r="O15" t="n">
-        <v>4.738354689739428</v>
+        <v>4.731054210112809</v>
       </c>
       <c r="P15" t="n">
-        <v>373.984655283687</v>
+        <v>374.0012723870206</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32749,28 +32867,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.176821488167172</v>
+        <v>0.1744389634395652</v>
       </c>
       <c r="J16" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K16" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08781689686202121</v>
+        <v>0.08614416280062975</v>
       </c>
       <c r="M16" t="n">
-        <v>3.538454966595282</v>
+        <v>3.535618186337143</v>
       </c>
       <c r="N16" t="n">
-        <v>17.86256669291658</v>
+        <v>17.83271234899697</v>
       </c>
       <c r="O16" t="n">
-        <v>4.226412981822361</v>
+        <v>4.222879627576066</v>
       </c>
       <c r="P16" t="n">
-        <v>374.6807878599446</v>
+        <v>374.706022134944</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32827,28 +32945,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2131422493082996</v>
+        <v>0.2080402499753207</v>
       </c>
       <c r="J17" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K17" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1153412106251329</v>
+        <v>0.1104001448752651</v>
       </c>
       <c r="M17" t="n">
-        <v>3.50387429266907</v>
+        <v>3.51514282977971</v>
       </c>
       <c r="N17" t="n">
-        <v>19.1646205285362</v>
+        <v>19.26630219972218</v>
       </c>
       <c r="O17" t="n">
-        <v>4.377741487175345</v>
+        <v>4.389339608611093</v>
       </c>
       <c r="P17" t="n">
-        <v>372.3315023143837</v>
+        <v>372.3855396356856</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -32905,28 +33023,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.154675371703428</v>
+        <v>0.1497621230799014</v>
       </c>
       <c r="J18" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K18" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05878706030749214</v>
+        <v>0.05534219745087088</v>
       </c>
       <c r="M18" t="n">
-        <v>3.688072693880292</v>
+        <v>3.692806620790806</v>
       </c>
       <c r="N18" t="n">
-        <v>21.0677582520384</v>
+        <v>21.14952738106853</v>
       </c>
       <c r="O18" t="n">
-        <v>4.589962772402234</v>
+        <v>4.598861530973566</v>
       </c>
       <c r="P18" t="n">
-        <v>374.2264043131363</v>
+        <v>374.2784424999682</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -32983,28 +33101,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1589975891910399</v>
+        <v>0.1536182194566351</v>
       </c>
       <c r="J19" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K19" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05791121475909033</v>
+        <v>0.05424894825502979</v>
       </c>
       <c r="M19" t="n">
-        <v>3.740223978110565</v>
+        <v>3.740197967681135</v>
       </c>
       <c r="N19" t="n">
-        <v>22.6193479664145</v>
+        <v>22.7273886263145</v>
       </c>
       <c r="O19" t="n">
-        <v>4.755980231920072</v>
+        <v>4.767325101806516</v>
       </c>
       <c r="P19" t="n">
-        <v>376.5694050245682</v>
+        <v>376.6263800870423</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33061,28 +33179,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.124801107923103</v>
+        <v>0.1204337125981112</v>
       </c>
       <c r="J20" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K20" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03809187270322778</v>
+        <v>0.0356441698428418</v>
       </c>
       <c r="M20" t="n">
-        <v>3.677644548674943</v>
+        <v>3.678859647089149</v>
       </c>
       <c r="N20" t="n">
-        <v>21.63256390637872</v>
+        <v>21.67821549108624</v>
       </c>
       <c r="O20" t="n">
-        <v>4.651082014583136</v>
+        <v>4.655987058732685</v>
       </c>
       <c r="P20" t="n">
-        <v>377.6301909287109</v>
+        <v>377.6764477643212</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33139,28 +33257,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1705561537164514</v>
+        <v>0.1662809724420115</v>
       </c>
       <c r="J21" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K21" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06771374860057588</v>
+        <v>0.06473748235358112</v>
       </c>
       <c r="M21" t="n">
-        <v>3.677110657029868</v>
+        <v>3.682572427161051</v>
       </c>
       <c r="N21" t="n">
-        <v>22.02810072925021</v>
+        <v>22.0669041832635</v>
       </c>
       <c r="O21" t="n">
-        <v>4.693410351679279</v>
+        <v>4.697542355664662</v>
       </c>
       <c r="P21" t="n">
-        <v>374.6357033679497</v>
+        <v>374.6809835275642</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33217,28 +33335,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2264067286349167</v>
+        <v>0.2231001020407292</v>
       </c>
       <c r="J22" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K22" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09903250848646905</v>
+        <v>0.09690411537092369</v>
       </c>
       <c r="M22" t="n">
-        <v>4.102445428586055</v>
+        <v>4.10279427686454</v>
       </c>
       <c r="N22" t="n">
-        <v>25.64955556614732</v>
+        <v>25.62534692845003</v>
       </c>
       <c r="O22" t="n">
-        <v>5.064539028001198</v>
+        <v>5.062148449862966</v>
       </c>
       <c r="P22" t="n">
-        <v>373.754090883293</v>
+        <v>373.7891126918104</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33295,28 +33413,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1982637995296845</v>
+        <v>0.1959104258033575</v>
       </c>
       <c r="J23" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K23" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08338786757335337</v>
+        <v>0.08207920978021799</v>
       </c>
       <c r="M23" t="n">
-        <v>3.995243306719424</v>
+        <v>3.991840101539944</v>
       </c>
       <c r="N23" t="n">
-        <v>23.76508799465064</v>
+        <v>23.71186484636502</v>
       </c>
       <c r="O23" t="n">
-        <v>4.874944922217137</v>
+        <v>4.869483016333974</v>
       </c>
       <c r="P23" t="n">
-        <v>376.6976301247159</v>
+        <v>376.7225556497685</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33373,28 +33491,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1842442592486468</v>
+        <v>0.1833585279845507</v>
       </c>
       <c r="J24" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K24" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06347708883157333</v>
+        <v>0.06338054979518559</v>
       </c>
       <c r="M24" t="n">
-        <v>4.200914756330376</v>
+        <v>4.189178202422004</v>
       </c>
       <c r="N24" t="n">
-        <v>27.54604032775282</v>
+        <v>27.44656325407559</v>
       </c>
       <c r="O24" t="n">
-        <v>5.248432178065448</v>
+        <v>5.23894676954019</v>
       </c>
       <c r="P24" t="n">
-        <v>376.5340210426704</v>
+        <v>376.5434021777474</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33451,28 +33569,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1764871667083538</v>
+        <v>0.1751097881075959</v>
       </c>
       <c r="J25" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K25" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06090416402527465</v>
+        <v>0.06045111532332048</v>
       </c>
       <c r="M25" t="n">
-        <v>4.073759252650709</v>
+        <v>4.064427676176889</v>
       </c>
       <c r="N25" t="n">
-        <v>26.41551210060922</v>
+        <v>26.32779467712313</v>
       </c>
       <c r="O25" t="n">
-        <v>5.139602329033757</v>
+        <v>5.131061749494263</v>
       </c>
       <c r="P25" t="n">
-        <v>376.3851179944417</v>
+        <v>376.3997063636565</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -33529,28 +33647,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1471742402396861</v>
+        <v>0.1439316974306921</v>
       </c>
       <c r="J26" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K26" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05053120705761305</v>
+        <v>0.04866897462832953</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75129956371273</v>
+        <v>3.752306972429268</v>
       </c>
       <c r="N26" t="n">
-        <v>22.38486457836223</v>
+        <v>22.37025487930381</v>
       </c>
       <c r="O26" t="n">
-        <v>4.731264585537595</v>
+        <v>4.729720380667742</v>
       </c>
       <c r="P26" t="n">
-        <v>380.4901296733424</v>
+        <v>380.5244727447874</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -33607,28 +33725,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1102870570211196</v>
+        <v>0.1072733583523702</v>
       </c>
       <c r="J27" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K27" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02719687473389976</v>
+        <v>0.02591089531141955</v>
       </c>
       <c r="M27" t="n">
-        <v>3.936064021243697</v>
+        <v>3.934640465046392</v>
       </c>
       <c r="N27" t="n">
-        <v>23.92901906994764</v>
+        <v>23.89893754177185</v>
       </c>
       <c r="O27" t="n">
-        <v>4.891729660349971</v>
+        <v>4.888653960117432</v>
       </c>
       <c r="P27" t="n">
-        <v>380.9102744883236</v>
+        <v>380.9421937796919</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -33685,28 +33803,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.159951189578786</v>
+        <v>0.1548649862467006</v>
       </c>
       <c r="J28" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K28" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04419873168627053</v>
+        <v>0.04164705203973673</v>
       </c>
       <c r="M28" t="n">
-        <v>4.526842133187027</v>
+        <v>4.52861088145706</v>
       </c>
       <c r="N28" t="n">
-        <v>30.43004453138933</v>
+        <v>30.48781273000883</v>
       </c>
       <c r="O28" t="n">
-        <v>5.5163434022357</v>
+        <v>5.521577014767505</v>
       </c>
       <c r="P28" t="n">
-        <v>382.6424193863425</v>
+        <v>382.6962894058632</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -33763,28 +33881,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1971409509959723</v>
+        <v>0.1918068370031708</v>
       </c>
       <c r="J29" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K29" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L29" t="n">
-        <v>0.07204957602752937</v>
+        <v>0.06854788365058562</v>
       </c>
       <c r="M29" t="n">
-        <v>4.334983061338107</v>
+        <v>4.343301649898168</v>
       </c>
       <c r="N29" t="n">
-        <v>27.53067650314107</v>
+        <v>27.61679169404572</v>
       </c>
       <c r="O29" t="n">
-        <v>5.246968315431404</v>
+        <v>5.255168093795452</v>
       </c>
       <c r="P29" t="n">
-        <v>386.6313818633614</v>
+        <v>386.6878776041245</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -33841,28 +33959,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.224936509670782</v>
+        <v>0.2195861091945169</v>
       </c>
       <c r="J30" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K30" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1251700454385276</v>
+        <v>0.1198176792547313</v>
       </c>
       <c r="M30" t="n">
-        <v>3.514955573078324</v>
+        <v>3.522585971419129</v>
       </c>
       <c r="N30" t="n">
-        <v>19.44970340086954</v>
+        <v>19.56771159810051</v>
       </c>
       <c r="O30" t="n">
-        <v>4.410181787735007</v>
+        <v>4.423540617887499</v>
       </c>
       <c r="P30" t="n">
-        <v>384.4886074922702</v>
+        <v>384.5452757297121</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -33919,28 +34037,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1686541223710787</v>
+        <v>0.1636272656334783</v>
       </c>
       <c r="J31" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K31" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L31" t="n">
-        <v>0.06679475729033946</v>
+        <v>0.06314672157542012</v>
       </c>
       <c r="M31" t="n">
-        <v>3.816202035353335</v>
+        <v>3.823049698602978</v>
       </c>
       <c r="N31" t="n">
-        <v>21.85740300230584</v>
+        <v>21.94374222305593</v>
       </c>
       <c r="O31" t="n">
-        <v>4.675190156807083</v>
+        <v>4.684414821838041</v>
       </c>
       <c r="P31" t="n">
-        <v>383.4171023574247</v>
+        <v>383.4703438133598</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -33997,28 +34115,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2072416111307513</v>
+        <v>0.2025843768043423</v>
       </c>
       <c r="J32" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K32" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08917820907377461</v>
+        <v>0.08572422317086026</v>
       </c>
       <c r="M32" t="n">
-        <v>3.817746676911829</v>
+        <v>3.824353936110075</v>
       </c>
       <c r="N32" t="n">
-        <v>24.12672808819072</v>
+        <v>24.18043608006364</v>
       </c>
       <c r="O32" t="n">
-        <v>4.911896587693059</v>
+        <v>4.917360682323765</v>
       </c>
       <c r="P32" t="n">
-        <v>395.2139344939966</v>
+        <v>395.2632611307227</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34075,28 +34193,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1341541744861846</v>
+        <v>0.1311064536868412</v>
       </c>
       <c r="J33" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K33" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02206399965852424</v>
+        <v>0.0212342559159272</v>
       </c>
       <c r="M33" t="n">
-        <v>4.836153498841488</v>
+        <v>4.833928109274848</v>
       </c>
       <c r="N33" t="n">
-        <v>43.87371583952162</v>
+        <v>43.76918181940601</v>
       </c>
       <c r="O33" t="n">
-        <v>6.623723714008731</v>
+        <v>6.615828128012851</v>
       </c>
       <c r="P33" t="n">
-        <v>377.9371468511888</v>
+        <v>377.9694264845882</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34134,7 +34252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH263"/>
+  <dimension ref="A1:AH264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79121,6 +79239,178 @@
         </is>
       </c>
     </row>
+    <row r="264">
+      <c r="A264" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-02 22:05:53+00:00</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>-36.58878809178883,175.524849923905</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>-36.589179554572745,175.52412128765175</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>-36.58968169127738,175.52351036596085</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>-36.590279671862916,175.52304846251192</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>-36.59097163560283,175.52288970171108</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>-36.59165360755824,175.52266037170057</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-36.59236390997333,175.52270343603547</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-36.59305542149075,175.52287266761758</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-36.59373304674061,175.5230653469494</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>-36.59439857910784,175.5233551031846</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>-36.59503974271006,175.52372138738522</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr">
+        <is>
+          <t>-36.5956568624899,175.52414878631197</t>
+        </is>
+      </c>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>-36.596275744323464,175.52457253407331</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>-36.59685004588763,175.52508947645745</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>-36.597407629777315,175.52563981323172</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>-36.597961808438754,175.52621188909336</t>
+        </is>
+      </c>
+      <c r="R264" t="inlineStr">
+        <is>
+          <t>-36.59849435315138,175.5268184607505</t>
+        </is>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>-36.59901164194755,175.5274383358459</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>-36.59950543593015,175.52808255914516</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>-36.60000223912924,175.52873003273933</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>-36.600476740981186,175.52940632433067</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>-36.60093640928417,175.5300878597791</t>
+        </is>
+      </c>
+      <c r="X264" t="inlineStr">
+        <is>
+          <t>-36.601361777310615,175.53079392275015</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>-36.60178207129313,175.53151761655096</t>
+        </is>
+      </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t>-36.60218655255835,175.53224911105366</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>-36.60254378852445,175.53301467872</t>
+        </is>
+      </c>
+      <c r="AB264" t="inlineStr">
+        <is>
+          <t>-36.60288519020341,175.53379601901221</t>
+        </is>
+      </c>
+      <c r="AC264" t="inlineStr">
+        <is>
+          <t>-36.60315075294787,175.5346053805323</t>
+        </is>
+      </c>
+      <c r="AD264" t="inlineStr">
+        <is>
+          <t>-36.60337790707136,175.53542932474346</t>
+        </is>
+      </c>
+      <c r="AE264" t="inlineStr">
+        <is>
+          <t>-36.60357463435451,175.5362846968994</t>
+        </is>
+      </c>
+      <c r="AF264" t="inlineStr">
+        <is>
+          <t>-36.60362500085438,175.53706054399163</t>
+        </is>
+      </c>
+      <c r="AG264" t="inlineStr">
+        <is>
+          <t>-36.60350783726271,175.53784560302117</t>
+        </is>
+      </c>
+      <c r="AH264" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH264"/>
+  <dimension ref="A1:AH265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28881,6 +28881,114 @@
         </is>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="n">
+        <v>382.37</v>
+      </c>
+      <c r="C265" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="D265" t="n">
+        <v>367.46</v>
+      </c>
+      <c r="E265" t="n">
+        <v>373.89</v>
+      </c>
+      <c r="F265" t="n">
+        <v>376.4</v>
+      </c>
+      <c r="G265" t="n">
+        <v>374.38</v>
+      </c>
+      <c r="H265" t="n">
+        <v>379.24</v>
+      </c>
+      <c r="I265" t="n">
+        <v>390.13</v>
+      </c>
+      <c r="J265" t="n">
+        <v>385.18</v>
+      </c>
+      <c r="K265" t="n">
+        <v>385.56</v>
+      </c>
+      <c r="L265" t="n">
+        <v>385.13</v>
+      </c>
+      <c r="M265" t="n">
+        <v>387.86</v>
+      </c>
+      <c r="N265" t="n">
+        <v>383.16</v>
+      </c>
+      <c r="O265" t="n">
+        <v>380.16</v>
+      </c>
+      <c r="P265" t="n">
+        <v>377.11</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>374.17</v>
+      </c>
+      <c r="R265" t="n">
+        <v>373.81</v>
+      </c>
+      <c r="S265" t="n">
+        <v>375.9</v>
+      </c>
+      <c r="T265" t="n">
+        <v>376.2</v>
+      </c>
+      <c r="U265" t="n">
+        <v>374.39</v>
+      </c>
+      <c r="V265" t="n">
+        <v>376.28</v>
+      </c>
+      <c r="W265" t="n">
+        <v>381.48</v>
+      </c>
+      <c r="X265" t="n">
+        <v>382.07</v>
+      </c>
+      <c r="Y265" t="n">
+        <v>380.87</v>
+      </c>
+      <c r="Z265" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="AA265" t="n">
+        <v>382.58</v>
+      </c>
+      <c r="AB265" t="n">
+        <v>382.35</v>
+      </c>
+      <c r="AC265" t="n">
+        <v>388.09</v>
+      </c>
+      <c r="AD265" t="n">
+        <v>384.24</v>
+      </c>
+      <c r="AE265" t="n">
+        <v>383.3</v>
+      </c>
+      <c r="AF265" t="n">
+        <v>398.19</v>
+      </c>
+      <c r="AG265" t="n">
+        <v>380.83</v>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28892,7 +29000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B270"/>
+  <dimension ref="A1:B271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31595,6 +31703,16 @@
       </c>
       <c r="B270" t="n">
         <v>0.39</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>-0.48</v>
       </c>
     </row>
   </sheetData>
@@ -31763,28 +31881,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1832889809826659</v>
+        <v>-0.1780726456037383</v>
       </c>
       <c r="J2" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K2" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03639943432694237</v>
+        <v>0.03457820493933794</v>
       </c>
       <c r="M2" t="n">
-        <v>5.579487417787073</v>
+        <v>5.58194193976353</v>
       </c>
       <c r="N2" t="n">
-        <v>47.76808819086664</v>
+        <v>47.76093956613654</v>
       </c>
       <c r="O2" t="n">
-        <v>6.911446172174578</v>
+        <v>6.910928994436025</v>
       </c>
       <c r="P2" t="n">
-        <v>380.4328225245234</v>
+        <v>380.3760949218658</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31841,28 +31959,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.253778395723105</v>
+        <v>-0.2472940114478498</v>
       </c>
       <c r="J3" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K3" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06700458842823964</v>
+        <v>0.06398729936293646</v>
       </c>
       <c r="M3" t="n">
-        <v>5.504132738916353</v>
+        <v>5.517449466904245</v>
       </c>
       <c r="N3" t="n">
-        <v>48.85046620274551</v>
+        <v>48.9422386984688</v>
       </c>
       <c r="O3" t="n">
-        <v>6.989310853206167</v>
+        <v>6.995872976153069</v>
       </c>
       <c r="P3" t="n">
-        <v>374.3624223206785</v>
+        <v>374.2925759811032</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -31919,28 +32037,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3883195878965702</v>
+        <v>-0.3830957594480767</v>
       </c>
       <c r="J4" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K4" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1033372872315323</v>
+        <v>0.1013731530677019</v>
       </c>
       <c r="M4" t="n">
-        <v>6.513236688893291</v>
+        <v>6.517330981683227</v>
       </c>
       <c r="N4" t="n">
-        <v>70.27702763285053</v>
+        <v>70.18348159586138</v>
       </c>
       <c r="O4" t="n">
-        <v>8.383139485470258</v>
+        <v>8.377558212024633</v>
       </c>
       <c r="P4" t="n">
-        <v>370.9687856484523</v>
+        <v>370.9119765587271</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -31997,28 +32115,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6272120794068381</v>
+        <v>-0.6227421231476334</v>
       </c>
       <c r="J5" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K5" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L5" t="n">
-        <v>0.165551470917314</v>
+        <v>0.1645484368269914</v>
       </c>
       <c r="M5" t="n">
-        <v>7.960041122347571</v>
+        <v>7.954904450205998</v>
       </c>
       <c r="N5" t="n">
-        <v>105.9487729027918</v>
+        <v>105.6675327686974</v>
       </c>
       <c r="O5" t="n">
-        <v>10.29314203257644</v>
+        <v>10.27947142457711</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7638390801141</v>
+        <v>384.7150048345642</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32075,28 +32193,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5773179821578374</v>
+        <v>-0.5710184565783597</v>
       </c>
       <c r="J6" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K6" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1109659527961968</v>
+        <v>0.1094448497653873</v>
       </c>
       <c r="M6" t="n">
-        <v>9.338088762214507</v>
+        <v>9.33587327217338</v>
       </c>
       <c r="N6" t="n">
-        <v>143.8476510622471</v>
+        <v>143.5538821590635</v>
       </c>
       <c r="O6" t="n">
-        <v>11.99365044772637</v>
+        <v>11.98139733750048</v>
       </c>
       <c r="P6" t="n">
-        <v>383.5018394657611</v>
+        <v>383.4335365028376</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32153,28 +32271,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6756873118093527</v>
+        <v>-0.6688166268327943</v>
       </c>
       <c r="J7" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K7" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05146880447223434</v>
+        <v>0.05084387591774453</v>
       </c>
       <c r="M7" t="n">
-        <v>16.88095883365991</v>
+        <v>16.84031784527143</v>
       </c>
       <c r="N7" t="n">
-        <v>450.2576514601075</v>
+        <v>448.8187832662882</v>
       </c>
       <c r="O7" t="n">
-        <v>21.21927546972581</v>
+        <v>21.18534359566274</v>
       </c>
       <c r="P7" t="n">
-        <v>383.4198755648755</v>
+        <v>383.3448893935209</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32235,28 +32353,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4548696333061872</v>
+        <v>0.4571741490720955</v>
       </c>
       <c r="J8" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K8" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03035737469909239</v>
+        <v>0.03089864573984313</v>
       </c>
       <c r="M8" t="n">
-        <v>14.89324646168774</v>
+        <v>14.84829307480332</v>
       </c>
       <c r="N8" t="n">
-        <v>356.9831344178612</v>
+        <v>355.6180960225433</v>
       </c>
       <c r="O8" t="n">
-        <v>18.89399731178824</v>
+        <v>18.85783911328505</v>
       </c>
       <c r="P8" t="n">
-        <v>364.1298619238306</v>
+        <v>364.104782915036</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32317,28 +32435,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6351904596725184</v>
+        <v>0.6374411245858146</v>
       </c>
       <c r="J9" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K9" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1186512505227907</v>
+        <v>0.1202319933453463</v>
       </c>
       <c r="M9" t="n">
-        <v>10.15145351613835</v>
+        <v>10.12531553716919</v>
       </c>
       <c r="N9" t="n">
-        <v>165.439577781397</v>
+        <v>164.8325985965885</v>
       </c>
       <c r="O9" t="n">
-        <v>12.8623317396729</v>
+        <v>12.83871483430442</v>
       </c>
       <c r="P9" t="n">
-        <v>370.2373697474468</v>
+        <v>370.2132919454504</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32399,28 +32517,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4166024116638564</v>
+        <v>0.4173955825804178</v>
       </c>
       <c r="J10" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K10" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1076284801779133</v>
+        <v>0.1087787167097459</v>
       </c>
       <c r="M10" t="n">
-        <v>7.006012500083153</v>
+        <v>6.983580369501327</v>
       </c>
       <c r="N10" t="n">
-        <v>79.19478966577257</v>
+        <v>78.89675855958467</v>
       </c>
       <c r="O10" t="n">
-        <v>8.899145445815153</v>
+        <v>8.882384733819217</v>
       </c>
       <c r="P10" t="n">
-        <v>373.035206318189</v>
+        <v>373.0267385328632</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32477,28 +32595,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.36784868847747</v>
+        <v>0.369192255945626</v>
       </c>
       <c r="J11" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K11" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1126840613000434</v>
+        <v>0.1142258390076228</v>
       </c>
       <c r="M11" t="n">
-        <v>6.109297630208819</v>
+        <v>6.093503207242595</v>
       </c>
       <c r="N11" t="n">
-        <v>57.37668742534845</v>
+        <v>57.167803312902</v>
       </c>
       <c r="O11" t="n">
-        <v>7.574740089623435</v>
+        <v>7.560939314192517</v>
       </c>
       <c r="P11" t="n">
-        <v>374.0089862913412</v>
+        <v>373.9944159526514</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32555,28 +32673,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.3993579985380245</v>
+        <v>0.401594089517731</v>
       </c>
       <c r="J12" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K12" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1357132092211084</v>
+        <v>0.1379348067143503</v>
       </c>
       <c r="M12" t="n">
-        <v>5.994873950038083</v>
+        <v>5.983731222812433</v>
       </c>
       <c r="N12" t="n">
-        <v>54.69426431924255</v>
+        <v>54.51657368457278</v>
       </c>
       <c r="O12" t="n">
-        <v>7.395557066187952</v>
+        <v>7.383533956349952</v>
       </c>
       <c r="P12" t="n">
-        <v>371.5720723043015</v>
+        <v>371.5478229802535</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32633,28 +32751,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2931383948091532</v>
+        <v>0.2966132738273391</v>
       </c>
       <c r="J13" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K13" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1037204583554792</v>
+        <v>0.1065267910577951</v>
       </c>
       <c r="M13" t="n">
-        <v>5.050209026103771</v>
+        <v>5.048936564832598</v>
       </c>
       <c r="N13" t="n">
-        <v>39.98579384378687</v>
+        <v>39.91090198332654</v>
       </c>
       <c r="O13" t="n">
-        <v>6.323432125340389</v>
+        <v>6.317507576831748</v>
       </c>
       <c r="P13" t="n">
-        <v>375.5063213565392</v>
+        <v>375.4686379759863</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32711,28 +32829,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1345234712462887</v>
+        <v>0.1356562889362906</v>
       </c>
       <c r="J14" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K14" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03393826987120618</v>
+        <v>0.0347574336053077</v>
       </c>
       <c r="M14" t="n">
-        <v>4.267751112060046</v>
+        <v>4.258523407113172</v>
       </c>
       <c r="N14" t="n">
-        <v>27.90915379392053</v>
+        <v>27.81067155930833</v>
       </c>
       <c r="O14" t="n">
-        <v>5.282911488367048</v>
+        <v>5.273582421780126</v>
       </c>
       <c r="P14" t="n">
-        <v>378.0860624750952</v>
+        <v>378.0738399256283</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32789,28 +32907,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2862089764703989</v>
+        <v>0.285122673629197</v>
       </c>
       <c r="J15" t="n">
+        <v>264</v>
+      </c>
+      <c r="K15" t="n">
         <v>263</v>
       </c>
-      <c r="K15" t="n">
-        <v>262</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.1684393039803077</v>
+        <v>0.1684666188008064</v>
       </c>
       <c r="M15" t="n">
-        <v>3.769690940868807</v>
+        <v>3.759344988864259</v>
       </c>
       <c r="N15" t="n">
-        <v>22.38287393902614</v>
+        <v>22.30577471060504</v>
       </c>
       <c r="O15" t="n">
-        <v>4.731054210112809</v>
+        <v>4.72289897315251</v>
       </c>
       <c r="P15" t="n">
-        <v>374.0012723870206</v>
+        <v>374.0128123573155</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32867,28 +32985,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1744389634395652</v>
+        <v>0.1727751036136489</v>
       </c>
       <c r="J16" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K16" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08614416280062975</v>
+        <v>0.08520047118786434</v>
       </c>
       <c r="M16" t="n">
-        <v>3.535618186337143</v>
+        <v>3.529569162156755</v>
       </c>
       <c r="N16" t="n">
-        <v>17.83271234899697</v>
+        <v>17.78388006618531</v>
       </c>
       <c r="O16" t="n">
-        <v>4.222879627576066</v>
+        <v>4.217093793856773</v>
       </c>
       <c r="P16" t="n">
-        <v>374.706022134944</v>
+        <v>374.7236955046057</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -32945,28 +33063,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2080402499753207</v>
+        <v>0.2052471141967218</v>
       </c>
       <c r="J17" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K17" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1104001448752651</v>
+        <v>0.1082961561179836</v>
       </c>
       <c r="M17" t="n">
-        <v>3.51514282977971</v>
+        <v>3.515281782307445</v>
       </c>
       <c r="N17" t="n">
-        <v>19.26630219972218</v>
+        <v>19.24606627419614</v>
       </c>
       <c r="O17" t="n">
-        <v>4.389339608611093</v>
+        <v>4.387033881131549</v>
       </c>
       <c r="P17" t="n">
-        <v>372.3855396356856</v>
+        <v>372.4152080731116</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33023,28 +33141,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1497621230799014</v>
+        <v>0.1464481340649657</v>
       </c>
       <c r="J18" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K18" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05534219745087088</v>
+        <v>0.05328291115895545</v>
       </c>
       <c r="M18" t="n">
-        <v>3.692806620790806</v>
+        <v>3.692035577402802</v>
       </c>
       <c r="N18" t="n">
-        <v>21.14952738106853</v>
+        <v>21.14366249519546</v>
       </c>
       <c r="O18" t="n">
-        <v>4.598861530973566</v>
+        <v>4.598223841353905</v>
       </c>
       <c r="P18" t="n">
-        <v>374.2784424999682</v>
+        <v>374.3136433936995</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33101,28 +33219,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1536182194566351</v>
+        <v>0.1500389299261625</v>
       </c>
       <c r="J19" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K19" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L19" t="n">
-        <v>0.05424894825502979</v>
+        <v>0.0520947088121021</v>
       </c>
       <c r="M19" t="n">
-        <v>3.740197967681135</v>
+        <v>3.735831095069987</v>
       </c>
       <c r="N19" t="n">
-        <v>22.7273886263145</v>
+        <v>22.72791046590381</v>
       </c>
       <c r="O19" t="n">
-        <v>4.767325101806516</v>
+        <v>4.76737983235066</v>
       </c>
       <c r="P19" t="n">
-        <v>376.6263800870423</v>
+        <v>376.6643989790265</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33179,28 +33297,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1204337125981112</v>
+        <v>0.1169474575190539</v>
       </c>
       <c r="J20" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K20" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0356441698428418</v>
+        <v>0.0338216325924402</v>
       </c>
       <c r="M20" t="n">
-        <v>3.678859647089149</v>
+        <v>3.67755859153849</v>
       </c>
       <c r="N20" t="n">
-        <v>21.67821549108624</v>
+        <v>21.67826755378792</v>
       </c>
       <c r="O20" t="n">
-        <v>4.655987058732685</v>
+        <v>4.655992649670735</v>
       </c>
       <c r="P20" t="n">
-        <v>377.6764477643212</v>
+        <v>377.7134784527167</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33257,28 +33375,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1662809724420115</v>
+        <v>0.1627749111773674</v>
       </c>
       <c r="J21" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K21" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06473748235358112</v>
+        <v>0.0624615016903517</v>
       </c>
       <c r="M21" t="n">
-        <v>3.682572427161051</v>
+        <v>3.684400396935033</v>
       </c>
       <c r="N21" t="n">
-        <v>22.0669041832635</v>
+        <v>22.06642020460742</v>
       </c>
       <c r="O21" t="n">
-        <v>4.697542355664662</v>
+        <v>4.697490841354289</v>
       </c>
       <c r="P21" t="n">
-        <v>374.6809835275642</v>
+        <v>374.7182245954845</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33335,28 +33453,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2231001020407292</v>
+        <v>0.220532905636837</v>
       </c>
       <c r="J22" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K22" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09690411537092369</v>
+        <v>0.09545095646780111</v>
       </c>
       <c r="M22" t="n">
-        <v>4.10279427686454</v>
+        <v>4.099508883103043</v>
       </c>
       <c r="N22" t="n">
-        <v>25.62534692845003</v>
+        <v>25.5728360452048</v>
       </c>
       <c r="O22" t="n">
-        <v>5.062148449862966</v>
+        <v>5.056959169817846</v>
       </c>
       <c r="P22" t="n">
-        <v>373.7891126918104</v>
+        <v>373.8163812214867</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33413,28 +33531,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1959104258033575</v>
+        <v>0.1955680769902312</v>
       </c>
       <c r="J23" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K23" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08207920978021799</v>
+        <v>0.08242965136034863</v>
       </c>
       <c r="M23" t="n">
-        <v>3.991840101539944</v>
+        <v>3.978417190581557</v>
       </c>
       <c r="N23" t="n">
-        <v>23.71186484636502</v>
+        <v>23.62283952127423</v>
       </c>
       <c r="O23" t="n">
-        <v>4.869483016333974</v>
+        <v>4.860333272654688</v>
       </c>
       <c r="P23" t="n">
-        <v>376.7225556497685</v>
+        <v>376.7261920481198</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33491,28 +33609,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1833585279845507</v>
+        <v>0.1838399953616212</v>
       </c>
       <c r="J24" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K24" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06338054979518559</v>
+        <v>0.06417836637715657</v>
       </c>
       <c r="M24" t="n">
-        <v>4.189178202422004</v>
+        <v>4.175875629104844</v>
       </c>
       <c r="N24" t="n">
-        <v>27.44656325407559</v>
+        <v>27.3441661482919</v>
       </c>
       <c r="O24" t="n">
-        <v>5.23894676954019</v>
+        <v>5.229164957074111</v>
       </c>
       <c r="P24" t="n">
-        <v>376.5434021777474</v>
+        <v>376.5382880745024</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33569,28 +33687,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1751097881075959</v>
+        <v>0.1749716061851121</v>
       </c>
       <c r="J25" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K25" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06045111532332048</v>
+        <v>0.0608264972294047</v>
       </c>
       <c r="M25" t="n">
-        <v>4.064427676176889</v>
+        <v>4.049643538083882</v>
       </c>
       <c r="N25" t="n">
-        <v>26.32779467712313</v>
+        <v>26.22819726809437</v>
       </c>
       <c r="O25" t="n">
-        <v>5.131061749494263</v>
+        <v>5.121347212218126</v>
       </c>
       <c r="P25" t="n">
-        <v>376.3997063636565</v>
+        <v>376.4011741196289</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -33647,28 +33765,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1439316974306921</v>
+        <v>0.1424415067834326</v>
       </c>
       <c r="J26" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K26" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L26" t="n">
-        <v>0.04866897462832953</v>
+        <v>0.04805620446811354</v>
       </c>
       <c r="M26" t="n">
-        <v>3.752306972429268</v>
+        <v>3.745073270811868</v>
       </c>
       <c r="N26" t="n">
-        <v>22.37025487930381</v>
+        <v>22.30053181409136</v>
       </c>
       <c r="O26" t="n">
-        <v>4.729720380667742</v>
+        <v>4.722343889859289</v>
       </c>
       <c r="P26" t="n">
-        <v>380.5244727447874</v>
+        <v>380.5403014160283</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -33725,28 +33843,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1072733583523702</v>
+        <v>0.1063693622954423</v>
       </c>
       <c r="J27" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K27" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02591089531141955</v>
+        <v>0.02568511577338761</v>
       </c>
       <c r="M27" t="n">
-        <v>3.934640465046392</v>
+        <v>3.923799025333115</v>
       </c>
       <c r="N27" t="n">
-        <v>23.89893754177185</v>
+        <v>23.81393597492289</v>
       </c>
       <c r="O27" t="n">
-        <v>4.888653960117432</v>
+        <v>4.879952456215418</v>
       </c>
       <c r="P27" t="n">
-        <v>380.9421937796919</v>
+        <v>380.9517959446327</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -33803,28 +33921,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1548649862467006</v>
+        <v>0.151537869072477</v>
       </c>
       <c r="J28" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K28" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04164705203973673</v>
+        <v>0.04016718052480195</v>
       </c>
       <c r="M28" t="n">
-        <v>4.52861088145706</v>
+        <v>4.523731820033974</v>
       </c>
       <c r="N28" t="n">
-        <v>30.48781273000883</v>
+        <v>30.4471649656411</v>
       </c>
       <c r="O28" t="n">
-        <v>5.521577014767505</v>
+        <v>5.517894975952433</v>
       </c>
       <c r="P28" t="n">
-        <v>382.6962894058632</v>
+        <v>382.7316297457236</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -33881,28 +33999,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1918068370031708</v>
+        <v>0.1890491664399011</v>
       </c>
       <c r="J29" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K29" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L29" t="n">
-        <v>0.06854788365058562</v>
+        <v>0.06711535489948073</v>
       </c>
       <c r="M29" t="n">
-        <v>4.343301649898168</v>
+        <v>4.339590537827724</v>
       </c>
       <c r="N29" t="n">
-        <v>27.61679169404572</v>
+        <v>27.56359425775107</v>
       </c>
       <c r="O29" t="n">
-        <v>5.255168093795452</v>
+        <v>5.250104213989573</v>
       </c>
       <c r="P29" t="n">
-        <v>386.6878776041245</v>
+        <v>386.7171693332179</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -33959,28 +34077,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2195861091945169</v>
+        <v>0.2150094550385745</v>
       </c>
       <c r="J30" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K30" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1198176792547313</v>
+        <v>0.115541412299179</v>
       </c>
       <c r="M30" t="n">
-        <v>3.522585971419129</v>
+        <v>3.527033098558573</v>
       </c>
       <c r="N30" t="n">
-        <v>19.56771159810051</v>
+        <v>19.63519457140699</v>
       </c>
       <c r="O30" t="n">
-        <v>4.423540617887499</v>
+        <v>4.431161763173061</v>
       </c>
       <c r="P30" t="n">
-        <v>384.5452757297121</v>
+        <v>384.593888539188</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34037,28 +34155,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1636272656334783</v>
+        <v>0.1602635141366459</v>
       </c>
       <c r="J31" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K31" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L31" t="n">
-        <v>0.06314672157542012</v>
+        <v>0.06100076760937567</v>
       </c>
       <c r="M31" t="n">
-        <v>3.823049698602978</v>
+        <v>3.823075446178942</v>
       </c>
       <c r="N31" t="n">
-        <v>21.94374222305593</v>
+        <v>21.93711545641101</v>
       </c>
       <c r="O31" t="n">
-        <v>4.684414821838041</v>
+        <v>4.68370744778226</v>
       </c>
       <c r="P31" t="n">
-        <v>383.4703438133598</v>
+        <v>383.5060732797053</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34115,28 +34233,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2025843768043423</v>
+        <v>0.2007492018745211</v>
       </c>
       <c r="J32" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K32" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08572422317086026</v>
+        <v>0.08486825854872349</v>
       </c>
       <c r="M32" t="n">
-        <v>3.824353936110075</v>
+        <v>3.818264786947455</v>
       </c>
       <c r="N32" t="n">
-        <v>24.18043608006364</v>
+        <v>24.11161186525242</v>
       </c>
       <c r="O32" t="n">
-        <v>4.917360682323765</v>
+        <v>4.910357610729836</v>
       </c>
       <c r="P32" t="n">
-        <v>395.2632611307227</v>
+        <v>395.2827541940346</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34193,28 +34311,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1311064536868412</v>
+        <v>0.1306418450740785</v>
       </c>
       <c r="J33" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K33" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0212342559159272</v>
+        <v>0.02125588782423393</v>
       </c>
       <c r="M33" t="n">
-        <v>4.833928109274848</v>
+        <v>4.818068743135143</v>
       </c>
       <c r="N33" t="n">
-        <v>43.76918181940601</v>
+        <v>43.60484878580075</v>
       </c>
       <c r="O33" t="n">
-        <v>6.615828128012851</v>
+        <v>6.603396761198039</v>
       </c>
       <c r="P33" t="n">
-        <v>377.9694264845882</v>
+        <v>377.9743615155526</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34252,7 +34370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH264"/>
+  <dimension ref="A1:AH265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79411,6 +79529,178 @@
         </is>
       </c>
     </row>
+    <row r="265">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>-36.58882195907066,175.52488162809271</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>-36.58918711652826,175.5241307120722</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>-36.58968830374919,175.5235220819099</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>-36.590293234396846,175.52308780846897</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>-36.59097394592947,175.52290359836078</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>-36.59165598067276,175.5227084350185</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>-36.59235968642669,175.52279646792945</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-36.59304499459166,175.52294821349162</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>-36.59371912198971,175.52311988282398</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>-36.59438613254421,175.5233930914397</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>-36.59502855683709,175.523749053416</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr">
+        <is>
+          <t>-36.59564472690282,175.52417415477564</t>
+        </is>
+      </c>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>-36.596260724363106,175.52459877312262</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>-36.596846430519456,175.5250949028476</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>-36.59740197960819,175.52564733419473</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>-36.59794318097037,175.5262361771263</t>
+        </is>
+      </c>
+      <c r="R265" t="inlineStr">
+        <is>
+          <t>-36.59848176270642,175.5268350661307</t>
+        </is>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>-36.598997025545046,175.5274565522776</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>-36.59949821765063,175.5280908168736</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>-36.59999590328206,175.52873700205012</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>-36.60047047251207,175.5294132195019</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>-36.60091785520629,175.53010667146103</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>-36.6013483684076,175.53080582045942</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>-36.60176985002881,175.53152791520364</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>-36.60216898106897,175.5322625206059</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>-36.602521837676036,175.53302940371674</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>-36.60286692069279,175.53380716758815</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>-36.60312253118163,175.53461864854518</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>-36.60336982090564,175.53543204659104</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>-36.60355603525198,175.53629008520338</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>-36.60359183985481,175.53705633170844</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>-36.60347994827039,175.53782988993902</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH265"/>
+  <dimension ref="A1:AH267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28989,6 +28989,222 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="n">
+        <v>382.72</v>
+      </c>
+      <c r="C266" t="n">
+        <v>375.98</v>
+      </c>
+      <c r="D266" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="E266" t="n">
+        <v>374.59</v>
+      </c>
+      <c r="F266" t="n">
+        <v>374.96</v>
+      </c>
+      <c r="G266" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="H266" t="n">
+        <v>377.77</v>
+      </c>
+      <c r="I266" t="n">
+        <v>390.41</v>
+      </c>
+      <c r="J266" t="n">
+        <v>385.26</v>
+      </c>
+      <c r="K266" t="n">
+        <v>386.38</v>
+      </c>
+      <c r="L266" t="n">
+        <v>386.02</v>
+      </c>
+      <c r="M266" t="n">
+        <v>387.86</v>
+      </c>
+      <c r="N266" t="n">
+        <v>382.97</v>
+      </c>
+      <c r="O266" t="n">
+        <v>380.36</v>
+      </c>
+      <c r="P266" t="n">
+        <v>377.35</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>375.31</v>
+      </c>
+      <c r="R266" t="n">
+        <v>374.84</v>
+      </c>
+      <c r="S266" t="n">
+        <v>376.4</v>
+      </c>
+      <c r="T266" t="n">
+        <v>376.86</v>
+      </c>
+      <c r="U266" t="n">
+        <v>375.63</v>
+      </c>
+      <c r="V266" t="n">
+        <v>376.7</v>
+      </c>
+      <c r="W266" t="n">
+        <v>382.23</v>
+      </c>
+      <c r="X266" t="n">
+        <v>382.52</v>
+      </c>
+      <c r="Y266" t="n">
+        <v>382.05</v>
+      </c>
+      <c r="Z266" t="n">
+        <v>383.47</v>
+      </c>
+      <c r="AA266" t="n">
+        <v>383.4</v>
+      </c>
+      <c r="AB266" t="n">
+        <v>383.76</v>
+      </c>
+      <c r="AC266" t="n">
+        <v>389.56</v>
+      </c>
+      <c r="AD266" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="AE266" t="n">
+        <v>384.66</v>
+      </c>
+      <c r="AF266" t="n">
+        <v>398.6</v>
+      </c>
+      <c r="AG266" t="n">
+        <v>381.58</v>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="n">
+        <v>382.72</v>
+      </c>
+      <c r="C267" t="n">
+        <v>375.98</v>
+      </c>
+      <c r="D267" t="n">
+        <v>367.71</v>
+      </c>
+      <c r="E267" t="n">
+        <v>373.27</v>
+      </c>
+      <c r="F267" t="n">
+        <v>371.77</v>
+      </c>
+      <c r="G267" t="n">
+        <v>374.47</v>
+      </c>
+      <c r="H267" t="n">
+        <v>377.77</v>
+      </c>
+      <c r="I267" t="n">
+        <v>386.94</v>
+      </c>
+      <c r="J267" t="n">
+        <v>383.35</v>
+      </c>
+      <c r="K267" t="n">
+        <v>385.78</v>
+      </c>
+      <c r="L267" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="M267" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="N267" t="n">
+        <v>382.8</v>
+      </c>
+      <c r="O267" t="n">
+        <v>380.29</v>
+      </c>
+      <c r="P267" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="R267" t="n">
+        <v>374.58</v>
+      </c>
+      <c r="S267" t="n">
+        <v>376.52</v>
+      </c>
+      <c r="T267" t="n">
+        <v>377.18</v>
+      </c>
+      <c r="U267" t="n">
+        <v>376.39</v>
+      </c>
+      <c r="V267" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="W267" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="X267" t="n">
+        <v>381.9</v>
+      </c>
+      <c r="Y267" t="n">
+        <v>381.8</v>
+      </c>
+      <c r="Z267" t="n">
+        <v>385.63</v>
+      </c>
+      <c r="AA267" t="n">
+        <v>383.45</v>
+      </c>
+      <c r="AB267" t="n">
+        <v>384.44</v>
+      </c>
+      <c r="AC267" t="n">
+        <v>388.7</v>
+      </c>
+      <c r="AD267" t="n">
+        <v>385.07</v>
+      </c>
+      <c r="AE267" t="n">
+        <v>383.9</v>
+      </c>
+      <c r="AF267" t="n">
+        <v>398.87</v>
+      </c>
+      <c r="AG267" t="n">
+        <v>382.74</v>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29000,7 +29216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B271"/>
+  <dimension ref="A1:B273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31713,6 +31929,26 @@
       </c>
       <c r="B271" t="n">
         <v>-0.48</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B272" t="n">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B273" t="n">
+        <v>-0.6</v>
       </c>
     </row>
   </sheetData>
@@ -31881,28 +32117,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1780726456037383</v>
+        <v>-0.1674051394544543</v>
       </c>
       <c r="J2" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K2" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03457820493933794</v>
+        <v>0.03093309439858327</v>
       </c>
       <c r="M2" t="n">
-        <v>5.58194193976353</v>
+        <v>5.587554105919707</v>
       </c>
       <c r="N2" t="n">
-        <v>47.76093956613654</v>
+        <v>47.77170475832703</v>
       </c>
       <c r="O2" t="n">
-        <v>6.910928994436025</v>
+        <v>6.911707803309326</v>
       </c>
       <c r="P2" t="n">
-        <v>380.3760949218658</v>
+        <v>380.2597570051832</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -31959,28 +32195,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2472940114478498</v>
+        <v>-0.2349872136437026</v>
       </c>
       <c r="J3" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K3" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06398729936293646</v>
+        <v>0.05845170562254143</v>
       </c>
       <c r="M3" t="n">
-        <v>5.517449466904245</v>
+        <v>5.540962033178172</v>
       </c>
       <c r="N3" t="n">
-        <v>48.9422386984688</v>
+        <v>49.08046152506228</v>
       </c>
       <c r="O3" t="n">
-        <v>6.995872976153069</v>
+        <v>7.005744894375064</v>
       </c>
       <c r="P3" t="n">
-        <v>374.2925759811032</v>
+        <v>374.1596332536241</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32037,28 +32273,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3830957594480767</v>
+        <v>-0.3725435158561032</v>
       </c>
       <c r="J4" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K4" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1013731530677019</v>
+        <v>0.09736078323032948</v>
       </c>
       <c r="M4" t="n">
-        <v>6.517330981683227</v>
+        <v>6.525649849855609</v>
       </c>
       <c r="N4" t="n">
-        <v>70.18348159586138</v>
+        <v>70.01432839454019</v>
       </c>
       <c r="O4" t="n">
-        <v>8.377558212024633</v>
+        <v>8.367456506880702</v>
       </c>
       <c r="P4" t="n">
-        <v>370.9119765587271</v>
+        <v>370.7968956036357</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32115,28 +32351,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6227421231476334</v>
+        <v>-0.613935632156693</v>
       </c>
       <c r="J5" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K5" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1645484368269914</v>
+        <v>0.1625463811888594</v>
       </c>
       <c r="M5" t="n">
-        <v>7.954904450205998</v>
+        <v>7.943758620861414</v>
       </c>
       <c r="N5" t="n">
-        <v>105.6675327686974</v>
+        <v>105.1132873172947</v>
       </c>
       <c r="O5" t="n">
-        <v>10.27947142457711</v>
+        <v>10.25247713078623</v>
       </c>
       <c r="P5" t="n">
-        <v>384.7150048345642</v>
+        <v>384.6185319052141</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32193,28 +32429,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5710184565783597</v>
+        <v>-0.563287728340127</v>
       </c>
       <c r="J6" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K6" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1094448497653873</v>
+        <v>0.1082324610785564</v>
       </c>
       <c r="M6" t="n">
-        <v>9.33587327217338</v>
+        <v>9.305828334828005</v>
       </c>
       <c r="N6" t="n">
-        <v>143.5538821590635</v>
+        <v>142.6760782024684</v>
       </c>
       <c r="O6" t="n">
-        <v>11.98139733750048</v>
+        <v>11.94470921380962</v>
       </c>
       <c r="P6" t="n">
-        <v>383.4335365028376</v>
+        <v>383.349502872097</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32271,28 +32507,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6688166268327943</v>
+        <v>-0.6552831245311352</v>
       </c>
       <c r="J7" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K7" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05084387591774453</v>
+        <v>0.04960688569359351</v>
       </c>
       <c r="M7" t="n">
-        <v>16.84031784527143</v>
+        <v>16.76009700874631</v>
       </c>
       <c r="N7" t="n">
-        <v>448.8187832662882</v>
+        <v>445.9702365848374</v>
       </c>
       <c r="O7" t="n">
-        <v>21.18534359566274</v>
+        <v>21.11800740090877</v>
       </c>
       <c r="P7" t="n">
-        <v>383.3448893935209</v>
+        <v>383.1967668541101</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32353,28 +32589,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4571741490720955</v>
+        <v>0.4593899392867544</v>
       </c>
       <c r="J8" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K8" t="n">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03089864573984313</v>
+        <v>0.03168300377268274</v>
       </c>
       <c r="M8" t="n">
-        <v>14.84829307480332</v>
+        <v>14.74550489442241</v>
       </c>
       <c r="N8" t="n">
-        <v>355.6180960225433</v>
+        <v>352.867032705622</v>
       </c>
       <c r="O8" t="n">
-        <v>18.85783911328505</v>
+        <v>18.78475532727595</v>
       </c>
       <c r="P8" t="n">
-        <v>364.104782915036</v>
+        <v>364.0806000573655</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32435,28 +32671,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6374411245858146</v>
+        <v>0.6395896245113037</v>
       </c>
       <c r="J9" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K9" t="n">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1202319933453463</v>
+        <v>0.1226461537160715</v>
       </c>
       <c r="M9" t="n">
-        <v>10.12531553716919</v>
+        <v>10.06238606601318</v>
       </c>
       <c r="N9" t="n">
-        <v>164.8325985965885</v>
+        <v>163.6040237695274</v>
       </c>
       <c r="O9" t="n">
-        <v>12.83871483430442</v>
+        <v>12.79077885703319</v>
       </c>
       <c r="P9" t="n">
-        <v>370.2132919454504</v>
+        <v>370.1902673235981</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32517,28 +32753,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4173955825804178</v>
+        <v>0.417597528001518</v>
       </c>
       <c r="J10" t="n">
+        <v>266</v>
+      </c>
+      <c r="K10" t="n">
         <v>264</v>
       </c>
-      <c r="K10" t="n">
-        <v>262</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1087787167097459</v>
+        <v>0.1104405607736982</v>
       </c>
       <c r="M10" t="n">
-        <v>6.983580369501327</v>
+        <v>6.938048481390771</v>
       </c>
       <c r="N10" t="n">
-        <v>78.89675855958467</v>
+        <v>78.30624868218629</v>
       </c>
       <c r="O10" t="n">
-        <v>8.882384733819217</v>
+        <v>8.849081798818807</v>
       </c>
       <c r="P10" t="n">
-        <v>373.0267385328632</v>
+        <v>373.0245911765788</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32595,28 +32831,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.369192255945626</v>
+        <v>0.3725408058275076</v>
       </c>
       <c r="J11" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K11" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1142258390076228</v>
+        <v>0.1176786467943843</v>
       </c>
       <c r="M11" t="n">
-        <v>6.093503207242595</v>
+        <v>6.066124144672038</v>
       </c>
       <c r="N11" t="n">
-        <v>57.167803312902</v>
+        <v>56.76938817993021</v>
       </c>
       <c r="O11" t="n">
-        <v>7.560939314192517</v>
+        <v>7.534546315467853</v>
       </c>
       <c r="P11" t="n">
-        <v>373.9944159526514</v>
+        <v>373.9580045215238</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32673,28 +32909,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.401594089517731</v>
+        <v>0.4067540561822652</v>
       </c>
       <c r="J12" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K12" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1379348067143503</v>
+        <v>0.1427827796624481</v>
       </c>
       <c r="M12" t="n">
-        <v>5.983731222812433</v>
+        <v>5.96551653186405</v>
       </c>
       <c r="N12" t="n">
-        <v>54.51657368457278</v>
+        <v>54.18963548795804</v>
       </c>
       <c r="O12" t="n">
-        <v>7.383533956349952</v>
+        <v>7.361360980685435</v>
       </c>
       <c r="P12" t="n">
-        <v>371.5478229802535</v>
+        <v>371.4917121368582</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32751,28 +32987,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.2966132738273391</v>
+        <v>0.303466465247029</v>
       </c>
       <c r="J13" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K13" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1065267910577951</v>
+        <v>0.1121794308211355</v>
       </c>
       <c r="M13" t="n">
-        <v>5.048936564832598</v>
+        <v>5.045714787150286</v>
       </c>
       <c r="N13" t="n">
-        <v>39.91090198332654</v>
+        <v>39.76223365493922</v>
       </c>
       <c r="O13" t="n">
-        <v>6.317507576831748</v>
+        <v>6.30573022376784</v>
       </c>
       <c r="P13" t="n">
-        <v>375.4686379759863</v>
+        <v>375.3941065436534</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -32829,28 +33065,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1356562889362906</v>
+        <v>0.1374318169936948</v>
       </c>
       <c r="J14" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K14" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0347574336053077</v>
+        <v>0.03619072410977986</v>
       </c>
       <c r="M14" t="n">
-        <v>4.258523407113172</v>
+        <v>4.237165384423857</v>
       </c>
       <c r="N14" t="n">
-        <v>27.81067155930833</v>
+        <v>27.6097911799875</v>
       </c>
       <c r="O14" t="n">
-        <v>5.273582421780126</v>
+        <v>5.254501991624658</v>
       </c>
       <c r="P14" t="n">
-        <v>378.0738399256283</v>
+        <v>378.0546297756302</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -32907,28 +33143,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.285122673629197</v>
+        <v>0.2832265689244916</v>
       </c>
       <c r="J15" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K15" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1684666188008064</v>
+        <v>0.1687788973936631</v>
       </c>
       <c r="M15" t="n">
-        <v>3.759344988864259</v>
+        <v>3.737824615039445</v>
       </c>
       <c r="N15" t="n">
-        <v>22.30577471060504</v>
+        <v>22.14983338935292</v>
       </c>
       <c r="O15" t="n">
-        <v>4.72289897315251</v>
+        <v>4.706360949752253</v>
       </c>
       <c r="P15" t="n">
-        <v>374.0128123573155</v>
+        <v>374.033013739501</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -32985,28 +33221,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1727751036136489</v>
+        <v>0.1700692543687382</v>
       </c>
       <c r="J16" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K16" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08520047118786434</v>
+        <v>0.08389700927054167</v>
       </c>
       <c r="M16" t="n">
-        <v>3.529569162156755</v>
+        <v>3.514807242829922</v>
       </c>
       <c r="N16" t="n">
-        <v>17.78388006618531</v>
+        <v>17.6754545917664</v>
       </c>
       <c r="O16" t="n">
-        <v>4.217093793856773</v>
+        <v>4.20421866602659</v>
       </c>
       <c r="P16" t="n">
-        <v>374.7236955046057</v>
+        <v>374.7525173497764</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33063,28 +33299,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2052471141967218</v>
+        <v>0.2017705068811501</v>
       </c>
       <c r="J17" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K17" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1082961561179836</v>
+        <v>0.1063614834869623</v>
       </c>
       <c r="M17" t="n">
-        <v>3.515281782307445</v>
+        <v>3.505640237722158</v>
       </c>
       <c r="N17" t="n">
-        <v>19.24606627419614</v>
+        <v>19.14317715251132</v>
       </c>
       <c r="O17" t="n">
-        <v>4.387033881131549</v>
+        <v>4.375291664850621</v>
       </c>
       <c r="P17" t="n">
-        <v>372.4152080731116</v>
+        <v>372.4522393997847</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33141,28 +33377,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1464481340649657</v>
+        <v>0.1413176900372891</v>
       </c>
       <c r="J18" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K18" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05328291115895545</v>
+        <v>0.05036167594843732</v>
       </c>
       <c r="M18" t="n">
-        <v>3.692035577402802</v>
+        <v>3.684909047295772</v>
       </c>
       <c r="N18" t="n">
-        <v>21.14366249519546</v>
+        <v>21.07522762146889</v>
       </c>
       <c r="O18" t="n">
-        <v>4.598223841353905</v>
+        <v>4.590776363695894</v>
       </c>
       <c r="P18" t="n">
-        <v>374.3136433936995</v>
+        <v>374.3682970638045</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33219,28 +33455,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1500389299261625</v>
+        <v>0.1438892866055379</v>
       </c>
       <c r="J19" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K19" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0520947088121021</v>
+        <v>0.04859239178167429</v>
       </c>
       <c r="M19" t="n">
-        <v>3.735831095069987</v>
+        <v>3.724295373398337</v>
       </c>
       <c r="N19" t="n">
-        <v>22.72791046590381</v>
+        <v>22.6869658936775</v>
       </c>
       <c r="O19" t="n">
-        <v>4.76737983235066</v>
+        <v>4.763083653860963</v>
       </c>
       <c r="P19" t="n">
-        <v>376.6643989790265</v>
+        <v>376.729906674905</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33297,28 +33533,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1169474575190539</v>
+        <v>0.1113749581835356</v>
       </c>
       <c r="J20" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K20" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0338216325924402</v>
+        <v>0.03110805019628093</v>
       </c>
       <c r="M20" t="n">
-        <v>3.67755859153849</v>
+        <v>3.670741835051591</v>
       </c>
       <c r="N20" t="n">
-        <v>21.67826755378792</v>
+        <v>21.62214721194565</v>
       </c>
       <c r="O20" t="n">
-        <v>4.655992649670735</v>
+        <v>4.649962065645875</v>
       </c>
       <c r="P20" t="n">
-        <v>377.7134784527167</v>
+        <v>377.7728366585666</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33375,28 +33611,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1627749111773674</v>
+        <v>0.1583127215557473</v>
       </c>
       <c r="J21" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K21" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0624615016903517</v>
+        <v>0.06001292120598578</v>
       </c>
       <c r="M21" t="n">
-        <v>3.684400396935033</v>
+        <v>3.676496340222541</v>
       </c>
       <c r="N21" t="n">
-        <v>22.06642020460742</v>
+        <v>21.96999215938991</v>
       </c>
       <c r="O21" t="n">
-        <v>4.697490841354289</v>
+        <v>4.687215821720812</v>
       </c>
       <c r="P21" t="n">
-        <v>374.7182245954845</v>
+        <v>374.7657520358756</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33453,28 +33689,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.220532905636837</v>
+        <v>0.2164003537999493</v>
       </c>
       <c r="J22" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K22" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09545095646780111</v>
+        <v>0.09339963524282557</v>
       </c>
       <c r="M22" t="n">
-        <v>4.099508883103043</v>
+        <v>4.088141986499543</v>
       </c>
       <c r="N22" t="n">
-        <v>25.5728360452048</v>
+        <v>25.43945468854785</v>
       </c>
       <c r="O22" t="n">
-        <v>5.056959169817846</v>
+        <v>5.043754027363731</v>
       </c>
       <c r="P22" t="n">
-        <v>373.8163812214867</v>
+        <v>373.8604003206995</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33531,28 +33767,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1955680769902312</v>
+        <v>0.1955628269315838</v>
       </c>
       <c r="J23" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K23" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08242965136034863</v>
+        <v>0.08365407103827427</v>
       </c>
       <c r="M23" t="n">
-        <v>3.978417190581557</v>
+        <v>3.950687537882618</v>
       </c>
       <c r="N23" t="n">
-        <v>23.62283952127423</v>
+        <v>23.44585865186403</v>
       </c>
       <c r="O23" t="n">
-        <v>4.860333272654688</v>
+        <v>4.842092383656474</v>
       </c>
       <c r="P23" t="n">
-        <v>376.7261920481198</v>
+        <v>376.7262523696306</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33609,28 +33845,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1838399953616212</v>
+        <v>0.1849615886937173</v>
       </c>
       <c r="J24" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K24" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06417836637715657</v>
+        <v>0.06588928429856755</v>
       </c>
       <c r="M24" t="n">
-        <v>4.175875629104844</v>
+        <v>4.150382968952663</v>
       </c>
       <c r="N24" t="n">
-        <v>27.3441661482919</v>
+        <v>27.14362292315979</v>
       </c>
       <c r="O24" t="n">
-        <v>5.229164957074111</v>
+        <v>5.209954215073275</v>
       </c>
       <c r="P24" t="n">
-        <v>376.5382880745024</v>
+        <v>376.5263450891137</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33687,28 +33923,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1749716061851121</v>
+        <v>0.1762258600144892</v>
       </c>
       <c r="J25" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K25" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0608264972294047</v>
+        <v>0.06257677721136123</v>
       </c>
       <c r="M25" t="n">
-        <v>4.049643538083882</v>
+        <v>4.02632361133263</v>
       </c>
       <c r="N25" t="n">
-        <v>26.22819726809437</v>
+        <v>26.03652069598689</v>
       </c>
       <c r="O25" t="n">
-        <v>5.121347212218126</v>
+        <v>5.102599405791806</v>
       </c>
       <c r="P25" t="n">
-        <v>376.4011741196289</v>
+        <v>376.3878152020125</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -33765,28 +34001,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1424415067834326</v>
+        <v>0.1427502135836581</v>
       </c>
       <c r="J26" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K26" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L26" t="n">
-        <v>0.04805620446811354</v>
+        <v>0.04898331740398587</v>
       </c>
       <c r="M26" t="n">
-        <v>3.745073270811868</v>
+        <v>3.725128104812603</v>
       </c>
       <c r="N26" t="n">
-        <v>22.30053181409136</v>
+        <v>22.1418869852597</v>
       </c>
       <c r="O26" t="n">
-        <v>4.722343889859289</v>
+        <v>4.705516654445046</v>
       </c>
       <c r="P26" t="n">
-        <v>380.5403014160283</v>
+        <v>380.5369966570194</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -33843,28 +34079,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1063693622954423</v>
+        <v>0.1058320296504904</v>
       </c>
       <c r="J27" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K27" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02568511577338761</v>
+        <v>0.02583544555887485</v>
       </c>
       <c r="M27" t="n">
-        <v>3.923799025333115</v>
+        <v>3.896677314592355</v>
       </c>
       <c r="N27" t="n">
-        <v>23.81393597492289</v>
+        <v>23.63587983442972</v>
       </c>
       <c r="O27" t="n">
-        <v>4.879952456215418</v>
+        <v>4.86167459158156</v>
       </c>
       <c r="P27" t="n">
-        <v>380.9517959446327</v>
+        <v>380.9575194893557</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -33921,28 +34157,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.151537869072477</v>
+        <v>0.1476265357046951</v>
       </c>
       <c r="J28" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K28" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L28" t="n">
-        <v>0.04016718052480195</v>
+        <v>0.03873097657205249</v>
       </c>
       <c r="M28" t="n">
-        <v>4.523731820033974</v>
+        <v>4.504080115165841</v>
       </c>
       <c r="N28" t="n">
-        <v>30.4471649656411</v>
+        <v>30.27167919955615</v>
       </c>
       <c r="O28" t="n">
-        <v>5.517894975952433</v>
+        <v>5.501970483341051</v>
       </c>
       <c r="P28" t="n">
-        <v>382.7316297457236</v>
+        <v>382.7732897795432</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -33999,28 +34235,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1890491664399011</v>
+        <v>0.1852012504463462</v>
       </c>
       <c r="J29" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K29" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L29" t="n">
-        <v>0.06711535489948073</v>
+        <v>0.06545207411819953</v>
       </c>
       <c r="M29" t="n">
-        <v>4.339590537827724</v>
+        <v>4.32485804759447</v>
       </c>
       <c r="N29" t="n">
-        <v>27.56359425775107</v>
+        <v>27.4086187012676</v>
       </c>
       <c r="O29" t="n">
-        <v>5.250104213989573</v>
+        <v>5.235324125712523</v>
       </c>
       <c r="P29" t="n">
-        <v>386.7171693332179</v>
+        <v>386.7581655663158</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34077,28 +34313,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2150094550385745</v>
+        <v>0.2074917591389141</v>
       </c>
       <c r="J30" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K30" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L30" t="n">
-        <v>0.115541412299179</v>
+        <v>0.1090692260971429</v>
       </c>
       <c r="M30" t="n">
-        <v>3.527033098558573</v>
+        <v>3.529432944482367</v>
       </c>
       <c r="N30" t="n">
-        <v>19.63519457140699</v>
+        <v>19.68178981245832</v>
       </c>
       <c r="O30" t="n">
-        <v>4.431161763173061</v>
+        <v>4.436416325420589</v>
       </c>
       <c r="P30" t="n">
-        <v>384.593888539188</v>
+        <v>384.6739719857827</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34155,28 +34391,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1602635141366459</v>
+        <v>0.1551427336954619</v>
       </c>
       <c r="J31" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K31" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L31" t="n">
-        <v>0.06100076760937567</v>
+        <v>0.05803664880621073</v>
       </c>
       <c r="M31" t="n">
-        <v>3.823075446178942</v>
+        <v>3.816390813778944</v>
       </c>
       <c r="N31" t="n">
-        <v>21.93711545641101</v>
+        <v>21.86329998453386</v>
       </c>
       <c r="O31" t="n">
-        <v>4.68370744778226</v>
+        <v>4.675820781909189</v>
       </c>
       <c r="P31" t="n">
-        <v>383.5060732797053</v>
+        <v>383.5606277249861</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34233,28 +34469,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.2007492018745211</v>
+        <v>0.197967842425352</v>
       </c>
       <c r="J32" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K32" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08486825854872349</v>
+        <v>0.08387492459910562</v>
       </c>
       <c r="M32" t="n">
-        <v>3.818264786947455</v>
+        <v>3.802108271040856</v>
       </c>
       <c r="N32" t="n">
-        <v>24.11161186525242</v>
+        <v>23.95703585922721</v>
       </c>
       <c r="O32" t="n">
-        <v>4.910357610729836</v>
+        <v>4.894592512071583</v>
       </c>
       <c r="P32" t="n">
-        <v>395.2827541940346</v>
+        <v>395.3123803840333</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34311,28 +34547,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1306418450740785</v>
+        <v>0.1316719376903592</v>
       </c>
       <c r="J33" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="K33" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02125588782423393</v>
+        <v>0.02192605632286637</v>
       </c>
       <c r="M33" t="n">
-        <v>4.818068743135143</v>
+        <v>4.786819580201552</v>
       </c>
       <c r="N33" t="n">
-        <v>43.60484878580075</v>
+        <v>43.28314133269644</v>
       </c>
       <c r="O33" t="n">
-        <v>6.603396761198039</v>
+        <v>6.578992425341166</v>
       </c>
       <c r="P33" t="n">
-        <v>377.9743615155526</v>
+        <v>377.9633797859121</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34370,7 +34606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH265"/>
+  <dimension ref="A1:AH267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -79701,6 +79937,350 @@
         </is>
       </c>
     </row>
+    <row r="266">
+      <c r="A266" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>-36.58882447574726,175.52488398403136</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>-36.589185782065584,175.52412904893905</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>-36.589689595247464,175.52352437018143</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>-36.59029571318746,175.5230949996375</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>-36.59097132634636,175.52288784152967</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>-36.591656030227135,175.52270943866088</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-36.59236043087002,175.52278007022258</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-36.59304456900294,175.52295129699618</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>-36.593718904415276,175.52312073494687</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>-36.594383351566535,175.52340157927694</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>-36.59502496281885,175.52375794249994</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr">
+        <is>
+          <t>-36.59564472690282,175.52417415477564</t>
+        </is>
+      </c>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>-36.59626171526343,175.52459704207456</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>-36.59684528278349,175.52509662551105</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>-36.59740050565097,175.5256492961849</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>-36.59793610253117,175.5262454065757</t>
+        </is>
+      </c>
+      <c r="R266" t="inlineStr">
+        <is>
+          <t>-36.598475405765264,175.5268434502177</t>
+        </is>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>-36.5989938480659,175.52746051237054</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>-36.59949384694902,175.52809581696528</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>-36.59998754535543,175.52874619560734</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>-36.60046764159041,175.52941633344983</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>-36.60091262379285,175.53011197550506</t>
+        </is>
+      </c>
+      <c r="X266" t="inlineStr">
+        <is>
+          <t>-36.6013450711362,175.53080874612502</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>-36.60176105667959,175.5315353252079</t>
+        </is>
+      </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t>-36.602160387152274,175.53226907898735</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>-36.60251533959065,175.53303376273948</t>
+        </is>
+      </c>
+      <c r="AB266" t="inlineStr">
+        <is>
+          <t>-36.602855522457844,175.53381412311302</t>
+        </is>
+      </c>
+      <c r="AC266" t="inlineStr">
+        <is>
+          <t>-36.60311014730172,175.53462447062552</t>
+        </is>
+      </c>
+      <c r="AD266" t="inlineStr">
+        <is>
+          <t>-36.60336060441561,175.5354351489113</t>
+        </is>
+      </c>
+      <c r="AE266" t="inlineStr">
+        <is>
+          <t>-36.603544103752135,175.53629354185</t>
+        </is>
+      </c>
+      <c r="AF266" t="inlineStr">
+        <is>
+          <t>-36.60358816525753,175.53705586494218</t>
+        </is>
+      </c>
+      <c r="AG266" t="inlineStr">
+        <is>
+          <t>-36.60347379628645,175.53782642381952</t>
+        </is>
+      </c>
+      <c r="AH266" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-30 22:05:16+00:00</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>-36.58882447574726,175.52488398403136</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>-36.589185782065584,175.52412904893905</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>-36.589689595247464,175.52352437018143</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>-36.59029103889618,175.52308143914865</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>-36.590965523234544,175.5228529357752</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>-36.591656030227135,175.52270943866088</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-36.59236043087002,175.52278007022258</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-36.5930498432576,175.5229130835618</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>-36.59372409900306,175.52310039051184</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>-36.5943853864283,175.52339536866435</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>-36.59502746651702,175.52375175010448</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>-36.5956438535081,175.52417598053594</t>
+        </is>
+      </c>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>-36.596262601858456,175.52459549324203</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>-36.596845684491086,175.52509602257885</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>-36.59739884744903,175.52565150342377</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>-36.59793361886815,175.52624864497864</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>-36.59847701043008,175.52684133384636</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>-36.59899308547089,175.52746146279281</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>-36.59949172782088,175.52809824125194</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>-36.599982422754906,175.52875183036724</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>-36.60046528248898,175.5294189284063</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>-36.60091666941925,175.53010787371105</t>
+        </is>
+      </c>
+      <c r="X267" t="inlineStr">
+        <is>
+          <t>-36.60134961404344,175.53080471520792</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>-36.60176291967734,175.53153375529186</t>
+        </is>
+      </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t>-36.6021438131692,175.53228172729044</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>-36.602514943365925,175.53303402853354</t>
+        </is>
+      </c>
+      <c r="AB267" t="inlineStr">
+        <is>
+          <t>-36.60285002543662,175.53381747754986</t>
+        </is>
+      </c>
+      <c r="AC267" t="inlineStr">
+        <is>
+          <t>-36.60311739229272,175.53462106451067</t>
+        </is>
+      </c>
+      <c r="AD267" t="inlineStr">
+        <is>
+          <t>-36.60336260422006,175.53543447576638</t>
+        </is>
+      </c>
+      <c r="AE267" t="inlineStr">
+        <is>
+          <t>-36.603550771354996,175.53629161019464</t>
+        </is>
+      </c>
+      <c r="AF267" t="inlineStr">
+        <is>
+          <t>-36.60358574540077,175.5370555575596</t>
+        </is>
+      </c>
+      <c r="AG267" t="inlineStr">
+        <is>
+          <t>-36.60346428121768,175.53782106288918</t>
+        </is>
+      </c>
+      <c r="AH267" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH267"/>
+  <dimension ref="A1:AH269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29119,7 +29119,7 @@
         <v>371.77</v>
       </c>
       <c r="G267" t="n">
-        <v>374.47</v>
+        <v>364.34</v>
       </c>
       <c r="H267" t="n">
         <v>377.77</v>
@@ -29200,6 +29200,222 @@
         <v>382.74</v>
       </c>
       <c r="AH267" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="n">
+        <v>380.06</v>
+      </c>
+      <c r="C268" t="n">
+        <v>372.67</v>
+      </c>
+      <c r="D268" t="n">
+        <v>364.68</v>
+      </c>
+      <c r="E268" t="n">
+        <v>371.55</v>
+      </c>
+      <c r="F268" t="n">
+        <v>368.91</v>
+      </c>
+      <c r="G268" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="H268" t="n">
+        <v>377.77</v>
+      </c>
+      <c r="I268" t="n">
+        <v>386.94</v>
+      </c>
+      <c r="J268" t="n">
+        <v>383.35</v>
+      </c>
+      <c r="K268" t="n">
+        <v>385.78</v>
+      </c>
+      <c r="L268" t="n">
+        <v>385.4</v>
+      </c>
+      <c r="M268" t="n">
+        <v>388.05</v>
+      </c>
+      <c r="N268" t="n">
+        <v>382.8</v>
+      </c>
+      <c r="O268" t="n">
+        <v>380.29</v>
+      </c>
+      <c r="P268" t="n">
+        <v>377.62</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>375.71</v>
+      </c>
+      <c r="R268" t="n">
+        <v>374.58</v>
+      </c>
+      <c r="S268" t="n">
+        <v>376.52</v>
+      </c>
+      <c r="T268" t="n">
+        <v>377.18</v>
+      </c>
+      <c r="U268" t="n">
+        <v>376.39</v>
+      </c>
+      <c r="V268" t="n">
+        <v>377.05</v>
+      </c>
+      <c r="W268" t="n">
+        <v>381.65</v>
+      </c>
+      <c r="X268" t="n">
+        <v>381.25</v>
+      </c>
+      <c r="Y268" t="n">
+        <v>381.21</v>
+      </c>
+      <c r="Z268" t="n">
+        <v>385.38</v>
+      </c>
+      <c r="AA268" t="n">
+        <v>383.07</v>
+      </c>
+      <c r="AB268" t="n">
+        <v>384.05</v>
+      </c>
+      <c r="AC268" t="n">
+        <v>387.89</v>
+      </c>
+      <c r="AD268" t="n">
+        <v>384.92</v>
+      </c>
+      <c r="AE268" t="n">
+        <v>382.98</v>
+      </c>
+      <c r="AF268" t="n">
+        <v>397.42</v>
+      </c>
+      <c r="AG268" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="n">
+        <v>377.38</v>
+      </c>
+      <c r="C269" t="n">
+        <v>369.85</v>
+      </c>
+      <c r="D269" t="n">
+        <v>362.86</v>
+      </c>
+      <c r="E269" t="n">
+        <v>371.74</v>
+      </c>
+      <c r="F269" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="G269" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="H269" t="n">
+        <v>373.79</v>
+      </c>
+      <c r="I269" t="n">
+        <v>385.56</v>
+      </c>
+      <c r="J269" t="n">
+        <v>382.83</v>
+      </c>
+      <c r="K269" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="L269" t="n">
+        <v>383.89</v>
+      </c>
+      <c r="M269" t="n">
+        <v>386.8</v>
+      </c>
+      <c r="N269" t="n">
+        <v>382.91</v>
+      </c>
+      <c r="O269" t="n">
+        <v>379.69</v>
+      </c>
+      <c r="P269" t="n">
+        <v>377.57</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>377.21</v>
+      </c>
+      <c r="R269" t="n">
+        <v>375.49</v>
+      </c>
+      <c r="S269" t="n">
+        <v>377.55</v>
+      </c>
+      <c r="T269" t="n">
+        <v>377.92</v>
+      </c>
+      <c r="U269" t="n">
+        <v>377.53</v>
+      </c>
+      <c r="V269" t="n">
+        <v>377.21</v>
+      </c>
+      <c r="W269" t="n">
+        <v>380.99</v>
+      </c>
+      <c r="X269" t="n">
+        <v>381.15</v>
+      </c>
+      <c r="Y269" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="Z269" t="n">
+        <v>386.07</v>
+      </c>
+      <c r="AA269" t="n">
+        <v>382.94</v>
+      </c>
+      <c r="AB269" t="n">
+        <v>384.99</v>
+      </c>
+      <c r="AC269" t="n">
+        <v>387.17</v>
+      </c>
+      <c r="AD269" t="n">
+        <v>385.41</v>
+      </c>
+      <c r="AE269" t="n">
+        <v>382.61</v>
+      </c>
+      <c r="AF269" t="n">
+        <v>397.08</v>
+      </c>
+      <c r="AG269" t="n">
+        <v>379.93</v>
+      </c>
+      <c r="AH269" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -29216,7 +29432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B273"/>
+  <dimension ref="A1:B275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31949,6 +32165,26 @@
       </c>
       <c r="B273" t="n">
         <v>-0.6</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B274" t="n">
+        <v>-0.09</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B275" t="n">
+        <v>0.19</v>
       </c>
     </row>
   </sheetData>
@@ -32117,28 +32353,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1674051394544543</v>
+        <v>-0.1630284253132006</v>
       </c>
       <c r="J2" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K2" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L2" t="n">
-        <v>0.03093309439858327</v>
+        <v>0.02980127859344261</v>
       </c>
       <c r="M2" t="n">
-        <v>5.587554105919707</v>
+        <v>5.564639357690011</v>
       </c>
       <c r="N2" t="n">
-        <v>47.77170475832703</v>
+        <v>47.48644517363163</v>
       </c>
       <c r="O2" t="n">
-        <v>6.911707803309326</v>
+        <v>6.891040935419817</v>
       </c>
       <c r="P2" t="n">
-        <v>380.2597570051832</v>
+        <v>380.2117747043774</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32195,28 +32431,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2349872136437026</v>
+        <v>-0.2300032330063237</v>
       </c>
       <c r="J3" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K3" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05845170562254143</v>
+        <v>0.05688392323199176</v>
       </c>
       <c r="M3" t="n">
-        <v>5.540962033178172</v>
+        <v>5.526032094957987</v>
       </c>
       <c r="N3" t="n">
-        <v>49.08046152506228</v>
+        <v>48.80901893400768</v>
       </c>
       <c r="O3" t="n">
-        <v>7.005744894375064</v>
+        <v>6.986345177130005</v>
       </c>
       <c r="P3" t="n">
-        <v>374.1596332536241</v>
+        <v>374.1055062476432</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32273,28 +32509,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3725435158561032</v>
+        <v>-0.3681459705526897</v>
       </c>
       <c r="J4" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K4" t="n">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09736078323032948</v>
+        <v>0.09660869867427979</v>
       </c>
       <c r="M4" t="n">
-        <v>6.525649849855609</v>
+        <v>6.499838615801806</v>
       </c>
       <c r="N4" t="n">
-        <v>70.01432839454019</v>
+        <v>69.55317611910127</v>
       </c>
       <c r="O4" t="n">
-        <v>8.367456506880702</v>
+        <v>8.339854682133332</v>
       </c>
       <c r="P4" t="n">
-        <v>370.7968956036357</v>
+        <v>370.7486781261704</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32351,28 +32587,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.613935632156693</v>
+        <v>-0.6087355779897102</v>
       </c>
       <c r="J5" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K5" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1625463811888594</v>
+        <v>0.1623176466275694</v>
       </c>
       <c r="M5" t="n">
-        <v>7.943758620861414</v>
+        <v>7.912507810762998</v>
       </c>
       <c r="N5" t="n">
-        <v>105.1132873172947</v>
+        <v>104.4013752434612</v>
       </c>
       <c r="O5" t="n">
-        <v>10.25247713078623</v>
+        <v>10.21769911689815</v>
       </c>
       <c r="P5" t="n">
-        <v>384.6185319052141</v>
+        <v>384.5612354381695</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32429,28 +32665,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.563287728340127</v>
+        <v>-0.5626121998673065</v>
       </c>
       <c r="J6" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K6" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1082324610785564</v>
+        <v>0.1095680445192635</v>
       </c>
       <c r="M6" t="n">
-        <v>9.305828334828005</v>
+        <v>9.238953654339731</v>
       </c>
       <c r="N6" t="n">
-        <v>142.6760782024684</v>
+        <v>141.5970157806165</v>
       </c>
       <c r="O6" t="n">
-        <v>11.94470921380962</v>
+        <v>11.89945443205765</v>
       </c>
       <c r="P6" t="n">
-        <v>383.349502872097</v>
+        <v>383.3421188464407</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32507,28 +32743,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6552831245311352</v>
+        <v>-0.6709353087226135</v>
       </c>
       <c r="J7" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K7" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04960688569359351</v>
+        <v>0.05269148731253492</v>
       </c>
       <c r="M7" t="n">
-        <v>16.76009700874631</v>
+        <v>16.66462705141598</v>
       </c>
       <c r="N7" t="n">
-        <v>445.9702365848374</v>
+        <v>442.4898724108945</v>
       </c>
       <c r="O7" t="n">
-        <v>21.11800740090877</v>
+        <v>21.03544324255837</v>
       </c>
       <c r="P7" t="n">
-        <v>383.1967668541101</v>
+        <v>383.368649690557</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32589,28 +32825,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4593899392867544</v>
+        <v>0.4584659182483625</v>
       </c>
       <c r="J8" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K8" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="L8" t="n">
-        <v>0.03168300377268274</v>
+        <v>0.0320537123733543</v>
       </c>
       <c r="M8" t="n">
-        <v>14.74550489442241</v>
+        <v>14.64652792229487</v>
       </c>
       <c r="N8" t="n">
-        <v>352.867032705622</v>
+        <v>350.175911313369</v>
       </c>
       <c r="O8" t="n">
-        <v>18.78475532727595</v>
+        <v>18.71298777088707</v>
       </c>
       <c r="P8" t="n">
-        <v>364.0806000573655</v>
+        <v>364.0907748637327</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32671,28 +32907,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6395896245113037</v>
+        <v>0.638001947078436</v>
       </c>
       <c r="J9" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K9" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1226461537160715</v>
+        <v>0.1238320846388387</v>
       </c>
       <c r="M9" t="n">
-        <v>10.06238606601318</v>
+        <v>9.992529212248515</v>
       </c>
       <c r="N9" t="n">
-        <v>163.6040237695274</v>
+        <v>162.3677187618482</v>
       </c>
       <c r="O9" t="n">
-        <v>12.79077885703319</v>
+        <v>12.7423592306075</v>
       </c>
       <c r="P9" t="n">
-        <v>370.1902673235981</v>
+        <v>370.2074128001746</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32753,28 +32989,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.417597528001518</v>
+        <v>0.4159515863836759</v>
       </c>
       <c r="J10" t="n">
+        <v>268</v>
+      </c>
+      <c r="K10" t="n">
         <v>266</v>
       </c>
-      <c r="K10" t="n">
-        <v>264</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1104405607736982</v>
+        <v>0.1112301416057765</v>
       </c>
       <c r="M10" t="n">
-        <v>6.938048481390771</v>
+        <v>6.893663430420591</v>
       </c>
       <c r="N10" t="n">
-        <v>78.30624868218629</v>
+        <v>77.72742796465295</v>
       </c>
       <c r="O10" t="n">
-        <v>8.849081798818807</v>
+        <v>8.816316008665577</v>
       </c>
       <c r="P10" t="n">
-        <v>373.0245911765788</v>
+        <v>373.042319507967</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -32831,28 +33067,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3725408058275076</v>
+        <v>0.3744774704651547</v>
       </c>
       <c r="J11" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K11" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1176786467943843</v>
+        <v>0.1204357492453187</v>
       </c>
       <c r="M11" t="n">
-        <v>6.066124144672038</v>
+        <v>6.031089250255714</v>
       </c>
       <c r="N11" t="n">
-        <v>56.76938817993021</v>
+        <v>56.35413745624919</v>
       </c>
       <c r="O11" t="n">
-        <v>7.534546315467853</v>
+        <v>7.506939286836492</v>
       </c>
       <c r="P11" t="n">
-        <v>373.9580045215238</v>
+        <v>373.9368314153491</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -32909,28 +33145,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4067540561822652</v>
+        <v>0.4100807255821205</v>
       </c>
       <c r="J12" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K12" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1427827796624481</v>
+        <v>0.1467063147058011</v>
       </c>
       <c r="M12" t="n">
-        <v>5.96551653186405</v>
+        <v>5.937713071437148</v>
       </c>
       <c r="N12" t="n">
-        <v>54.18963548795804</v>
+        <v>53.82086901071844</v>
       </c>
       <c r="O12" t="n">
-        <v>7.361360980685435</v>
+        <v>7.336270783628317</v>
       </c>
       <c r="P12" t="n">
-        <v>371.4917121368582</v>
+        <v>371.4553400507476</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -32987,28 +33223,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.303466465247029</v>
+        <v>0.3092331400897142</v>
       </c>
       <c r="J13" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K13" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1121794308211355</v>
+        <v>0.1173511240629461</v>
       </c>
       <c r="M13" t="n">
-        <v>5.045714787150286</v>
+        <v>5.037338376027836</v>
       </c>
       <c r="N13" t="n">
-        <v>39.76223365493922</v>
+        <v>39.57628699334884</v>
       </c>
       <c r="O13" t="n">
-        <v>6.30573022376784</v>
+        <v>6.290968684817057</v>
       </c>
       <c r="P13" t="n">
-        <v>375.3941065436534</v>
+        <v>375.3310461314438</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33065,28 +33301,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1374318169936948</v>
+        <v>0.1390773547430631</v>
       </c>
       <c r="J14" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K14" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03619072410977986</v>
+        <v>0.03759858124849902</v>
       </c>
       <c r="M14" t="n">
-        <v>4.237165384423857</v>
+        <v>4.21522317514699</v>
       </c>
       <c r="N14" t="n">
-        <v>27.6097911799875</v>
+        <v>27.41063777108068</v>
       </c>
       <c r="O14" t="n">
-        <v>5.254501991624658</v>
+        <v>5.235516953566351</v>
       </c>
       <c r="P14" t="n">
-        <v>378.0546297756302</v>
+        <v>378.036722581963</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33143,28 +33379,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2832265689244916</v>
+        <v>0.2808577972963023</v>
       </c>
       <c r="J15" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K15" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1687788973936631</v>
+        <v>0.1685399060435334</v>
       </c>
       <c r="M15" t="n">
-        <v>3.737824615039445</v>
+        <v>3.718181443333791</v>
       </c>
       <c r="N15" t="n">
-        <v>22.14983338935292</v>
+        <v>22.0042636776688</v>
       </c>
       <c r="O15" t="n">
-        <v>4.706360949752253</v>
+        <v>4.690870247370823</v>
       </c>
       <c r="P15" t="n">
-        <v>374.033013739501</v>
+        <v>374.0584010438703</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33221,28 +33457,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1700692543687382</v>
+        <v>0.1675877977416821</v>
       </c>
       <c r="J16" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K16" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08389700927054167</v>
+        <v>0.08278357595319918</v>
       </c>
       <c r="M16" t="n">
-        <v>3.514807242829922</v>
+        <v>3.499203335992612</v>
       </c>
       <c r="N16" t="n">
-        <v>17.6754545917664</v>
+        <v>17.56503982070706</v>
       </c>
       <c r="O16" t="n">
-        <v>4.20421866602659</v>
+        <v>4.191066668606819</v>
       </c>
       <c r="P16" t="n">
-        <v>374.7525173497764</v>
+        <v>374.7791035151135</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33299,28 +33535,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2017705068811501</v>
+        <v>0.1997481465727598</v>
       </c>
       <c r="J17" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K17" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1063614834869623</v>
+        <v>0.1058804079023793</v>
       </c>
       <c r="M17" t="n">
-        <v>3.505640237722158</v>
+        <v>3.489103890128492</v>
       </c>
       <c r="N17" t="n">
-        <v>19.14317715251132</v>
+        <v>19.01876150887069</v>
       </c>
       <c r="O17" t="n">
-        <v>4.375291664850621</v>
+        <v>4.361050505196046</v>
       </c>
       <c r="P17" t="n">
-        <v>372.4522393997847</v>
+        <v>372.4738953842699</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33377,28 +33613,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1413176900372891</v>
+        <v>0.1368080923793877</v>
       </c>
       <c r="J18" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K18" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05036167594843732</v>
+        <v>0.04791941065924998</v>
       </c>
       <c r="M18" t="n">
-        <v>3.684909047295772</v>
+        <v>3.675387795141954</v>
       </c>
       <c r="N18" t="n">
-        <v>21.07522762146889</v>
+        <v>20.99048762476536</v>
       </c>
       <c r="O18" t="n">
-        <v>4.590776363695894</v>
+        <v>4.581537692169012</v>
       </c>
       <c r="P18" t="n">
-        <v>374.3682970638045</v>
+        <v>374.4166051299916</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33455,28 +33691,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1438892866055379</v>
+        <v>0.1387555304235288</v>
       </c>
       <c r="J19" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K19" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04859239178167429</v>
+        <v>0.04585834904708663</v>
       </c>
       <c r="M19" t="n">
-        <v>3.724295373398337</v>
+        <v>3.709957895260437</v>
       </c>
       <c r="N19" t="n">
-        <v>22.6869658936775</v>
+        <v>22.61162389771398</v>
       </c>
       <c r="O19" t="n">
-        <v>4.763083653860963</v>
+        <v>4.75516812507339</v>
       </c>
       <c r="P19" t="n">
-        <v>376.729906674905</v>
+        <v>376.7849009841709</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33533,28 +33769,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1113749581835356</v>
+        <v>0.106737589198185</v>
       </c>
       <c r="J20" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K20" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L20" t="n">
-        <v>0.03110805019628093</v>
+        <v>0.02899418079644622</v>
       </c>
       <c r="M20" t="n">
-        <v>3.670741835051591</v>
+        <v>3.661479473794754</v>
       </c>
       <c r="N20" t="n">
-        <v>21.62214721194565</v>
+        <v>21.53686468202043</v>
       </c>
       <c r="O20" t="n">
-        <v>4.649962065645875</v>
+        <v>4.640782766088112</v>
       </c>
       <c r="P20" t="n">
-        <v>377.7728366585666</v>
+        <v>377.8225149424106</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33611,28 +33847,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1583127215557473</v>
+        <v>0.1553485407478193</v>
       </c>
       <c r="J21" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K21" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L21" t="n">
-        <v>0.06001292120598578</v>
+        <v>0.05871340697835936</v>
       </c>
       <c r="M21" t="n">
-        <v>3.676496340222541</v>
+        <v>3.661992136940862</v>
       </c>
       <c r="N21" t="n">
-        <v>21.96999215938991</v>
+        <v>21.83914629580255</v>
       </c>
       <c r="O21" t="n">
-        <v>4.687215821720812</v>
+        <v>4.673237239409374</v>
       </c>
       <c r="P21" t="n">
-        <v>374.7657520358756</v>
+        <v>374.7975011117557</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33689,28 +33925,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2164003537999493</v>
+        <v>0.2127413472423596</v>
       </c>
       <c r="J22" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K22" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L22" t="n">
-        <v>0.09339963524282557</v>
+        <v>0.0917272608516333</v>
       </c>
       <c r="M22" t="n">
-        <v>4.088141986499543</v>
+        <v>4.07451305974072</v>
       </c>
       <c r="N22" t="n">
-        <v>25.43945468854785</v>
+        <v>25.29637993468697</v>
       </c>
       <c r="O22" t="n">
-        <v>5.043754027363731</v>
+        <v>5.029550669263307</v>
       </c>
       <c r="P22" t="n">
-        <v>373.8604003206995</v>
+        <v>373.8996009412479</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -33767,28 +34003,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1955628269315838</v>
+        <v>0.1946299300922934</v>
       </c>
       <c r="J23" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K23" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08365407103827427</v>
+        <v>0.08413954689076375</v>
       </c>
       <c r="M23" t="n">
-        <v>3.950687537882618</v>
+        <v>3.925863145029535</v>
       </c>
       <c r="N23" t="n">
-        <v>23.44585865186403</v>
+        <v>23.27475410267154</v>
       </c>
       <c r="O23" t="n">
-        <v>4.842092383656474</v>
+        <v>4.824391578496872</v>
       </c>
       <c r="P23" t="n">
-        <v>376.7262523696306</v>
+        <v>376.7362522187404</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -33845,28 +34081,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1849615886937173</v>
+        <v>0.1845504535849491</v>
       </c>
       <c r="J24" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K24" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06588928429856755</v>
+        <v>0.06660515244121246</v>
       </c>
       <c r="M24" t="n">
-        <v>4.150382968952663</v>
+        <v>4.121431911405684</v>
       </c>
       <c r="N24" t="n">
-        <v>27.14362292315979</v>
+        <v>26.94167028291633</v>
       </c>
       <c r="O24" t="n">
-        <v>5.209954215073275</v>
+        <v>5.190536608378398</v>
       </c>
       <c r="P24" t="n">
-        <v>376.5263450891137</v>
+        <v>376.5307507174499</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -33923,28 +34159,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1762258600144892</v>
+        <v>0.1761299579233858</v>
       </c>
       <c r="J25" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K25" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06257677721136123</v>
+        <v>0.06345936709845679</v>
       </c>
       <c r="M25" t="n">
-        <v>4.02632361133263</v>
+        <v>3.997513532705304</v>
       </c>
       <c r="N25" t="n">
-        <v>26.03652069598689</v>
+        <v>25.84247240311252</v>
       </c>
       <c r="O25" t="n">
-        <v>5.102599405791806</v>
+        <v>5.083549193537181</v>
       </c>
       <c r="P25" t="n">
-        <v>376.3878152020125</v>
+        <v>376.3888452567579</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34001,28 +34237,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1427502135836581</v>
+        <v>0.1447245390153295</v>
       </c>
       <c r="J26" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K26" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L26" t="n">
-        <v>0.04898331740398587</v>
+        <v>0.05101893583453321</v>
       </c>
       <c r="M26" t="n">
-        <v>3.725128104812603</v>
+        <v>3.708094582547649</v>
       </c>
       <c r="N26" t="n">
-        <v>22.1418869852597</v>
+        <v>21.99111304947839</v>
       </c>
       <c r="O26" t="n">
-        <v>4.705516654445046</v>
+        <v>4.689468312024125</v>
       </c>
       <c r="P26" t="n">
-        <v>380.5369966570194</v>
+        <v>380.5158390490193</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34079,28 +34315,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1058320296504904</v>
+        <v>0.1046858873791875</v>
       </c>
       <c r="J27" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K27" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02583544555887485</v>
+        <v>0.02568665537079917</v>
       </c>
       <c r="M27" t="n">
-        <v>3.896677314592355</v>
+        <v>3.872629329554486</v>
       </c>
       <c r="N27" t="n">
-        <v>23.63587983442972</v>
+        <v>23.46410966637649</v>
       </c>
       <c r="O27" t="n">
-        <v>4.86167459158156</v>
+        <v>4.843976637678643</v>
       </c>
       <c r="P27" t="n">
-        <v>380.9575194893557</v>
+        <v>380.9698000205578</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34157,28 +34393,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1476265357046951</v>
+        <v>0.1444323919510855</v>
       </c>
       <c r="J28" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K28" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L28" t="n">
-        <v>0.03873097657205249</v>
+        <v>0.03766773453060279</v>
       </c>
       <c r="M28" t="n">
-        <v>4.504080115165841</v>
+        <v>4.482160082027202</v>
       </c>
       <c r="N28" t="n">
-        <v>30.27167919955615</v>
+        <v>30.08302218667712</v>
       </c>
       <c r="O28" t="n">
-        <v>5.501970483341051</v>
+        <v>5.484799192921936</v>
       </c>
       <c r="P28" t="n">
-        <v>382.7732897795432</v>
+        <v>382.8075041701213</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34235,28 +34471,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1852012504463462</v>
+        <v>0.17914258488615</v>
       </c>
       <c r="J29" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K29" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L29" t="n">
-        <v>0.06545207411819953</v>
+        <v>0.06215499510647671</v>
       </c>
       <c r="M29" t="n">
-        <v>4.32485804759447</v>
+        <v>4.320541882129962</v>
       </c>
       <c r="N29" t="n">
-        <v>27.4086187012676</v>
+        <v>27.3331331103238</v>
       </c>
       <c r="O29" t="n">
-        <v>5.235324125712523</v>
+        <v>5.228109898455062</v>
       </c>
       <c r="P29" t="n">
-        <v>386.7581655663158</v>
+        <v>386.8230822619572</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34313,28 +34549,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2074917591389141</v>
+        <v>0.2001635339707055</v>
       </c>
       <c r="J30" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K30" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1090692260971429</v>
+        <v>0.1028711134962443</v>
       </c>
       <c r="M30" t="n">
-        <v>3.529432944482367</v>
+        <v>3.531402399515127</v>
       </c>
       <c r="N30" t="n">
-        <v>19.68178981245832</v>
+        <v>19.72277546377347</v>
       </c>
       <c r="O30" t="n">
-        <v>4.436416325420589</v>
+        <v>4.441033152744243</v>
       </c>
       <c r="P30" t="n">
-        <v>384.6739719857827</v>
+        <v>384.7524814053068</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34391,28 +34627,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1551427336954619</v>
+        <v>0.1480299110082204</v>
       </c>
       <c r="J31" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K31" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L31" t="n">
-        <v>0.05803664880621073</v>
+        <v>0.05351354770964312</v>
       </c>
       <c r="M31" t="n">
-        <v>3.816390813778944</v>
+        <v>3.818059510042123</v>
       </c>
       <c r="N31" t="n">
-        <v>21.86329998453386</v>
+        <v>21.87692736036041</v>
       </c>
       <c r="O31" t="n">
-        <v>4.675820781909189</v>
+        <v>4.677277772418527</v>
       </c>
       <c r="P31" t="n">
-        <v>383.5606277249861</v>
+        <v>383.6368357541767</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34469,28 +34705,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.197967842425352</v>
+        <v>0.193101751899338</v>
       </c>
       <c r="J32" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K32" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08387492459910562</v>
+        <v>0.08105989805854252</v>
       </c>
       <c r="M32" t="n">
-        <v>3.802108271040856</v>
+        <v>3.795600923775449</v>
       </c>
       <c r="N32" t="n">
-        <v>23.95703585922721</v>
+        <v>23.86109057194438</v>
       </c>
       <c r="O32" t="n">
-        <v>4.894592512071583</v>
+        <v>4.884781527555186</v>
       </c>
       <c r="P32" t="n">
-        <v>395.3123803840333</v>
+        <v>395.3645172011804</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34547,28 +34783,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1316719376903592</v>
+        <v>0.1298902181564372</v>
       </c>
       <c r="J33" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="K33" t="n">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02192605632286637</v>
+        <v>0.02168123287903634</v>
       </c>
       <c r="M33" t="n">
-        <v>4.786819580201552</v>
+        <v>4.760610404213618</v>
       </c>
       <c r="N33" t="n">
-        <v>43.28314133269644</v>
+        <v>42.9720441536019</v>
       </c>
       <c r="O33" t="n">
-        <v>6.578992425341166</v>
+        <v>6.555306564425641</v>
       </c>
       <c r="P33" t="n">
-        <v>377.9633797859121</v>
+        <v>377.9824737691529</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34606,7 +34842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH267"/>
+  <dimension ref="A1:AH269"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80142,7 +80378,7 @@
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>-36.591656030227135,175.52270943866088</t>
+          <t>-36.591650452552116,175.52259647313917</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -80276,6 +80512,350 @@
         </is>
       </c>
       <c r="AH267" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-01 22:05:05+00:00</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>-36.588805349003714,175.5248660789016</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>-36.58916474838856,175.52410283480026</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>-36.5896739422854,175.52349663633552</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-36.59028494815057,175.52306376942315</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-36.59096032043576,175.52282164096485</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-36.59164795274964,175.52254584496188</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-36.59236043087002,175.52278007022258</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-36.5930498432576,175.5229130835618</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>-36.59372409900306,175.52310039051184</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>-36.5943853864283,175.52339536866435</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>-36.59502746651702,175.52375175010448</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>-36.5956438535081,175.52417598053594</t>
+        </is>
+      </c>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>-36.596262601858456,175.52459549324203</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>-36.596845684491086,175.52509602257885</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>-36.59739884744903,175.52565150342377</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>-36.59793361886815,175.52624864497864</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>-36.59847701043008,175.52684133384636</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>-36.59899308547089,175.52746146279281</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>-36.59949172782088,175.52809824125194</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>-36.599982422754906,175.52875183036724</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>-36.60046528248898,175.5294189284063</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>-36.60091666941925,175.53010787371105</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>-36.60135437676864,175.53080048924593</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>-36.60176731635195,175.53153005028977</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>-36.60214573145433,175.53228026336674</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>-36.60251795467381,175.53303200849874</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>-36.60285317813997,175.53381555368173</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>-36.60312421606322,175.53461785642526</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>-36.60336390844034,175.53543403675883</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>-36.60355884266369,175.53628927187464</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>-36.60359874092772,175.53705720831834</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>-36.60348183487877,175.53783095288242</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:04:44+00:00</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>-36.58878607844693,175.52484803915587</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>-36.58914682845326,175.52408050131564</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>-36.589664540172855,175.52347997772708</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-36.59028562096562,175.5230657213113</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-36.59095957457931,175.5228171546462</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-36.591648338183155,175.5225536510684</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>-36.592362446426385,175.5227356737078</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>-36.59305194079644,175.52289788628656</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>-36.5937255132358,175.52309485171227</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>-36.59438894743563,175.52338450009157</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>-36.595033564232246,175.52373666862346</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>-36.59564959952552,175.52416396895407</t>
+        </is>
+      </c>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>-36.59626202817934,175.52459649542777</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>-36.5968491276989,175.5250908545883</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>-36.597399154523465,175.52565109467582</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>-36.597924305131066,175.5262607889877</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>-36.59847139410309,175.52684874114564</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>-36.59898653986341,175.52746962058308</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>-36.59948682733694,175.5281038474144</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>-36.599974738853675,175.52876028250571</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>-36.6004642040426,175.52942011467204</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>-36.60092127306292,175.53010320615186</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>-36.60135510949559,175.53079983909788</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>-36.60176977550889,175.5315279780003</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>-36.60214043698731,175.53228430379596</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>-36.60251898485808,175.53303131743414</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>-36.60284557931643,175.53382019069696</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>-36.60313028163694,175.53461500479327</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>-36.6033596479874,175.53543547085016</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>-36.60356208873349,175.5362883314632</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>-36.60360178815472,175.5370575953929</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>-36.603487330650964,175.53783404928313</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
         <is>
           <t>L8</t>
         </is>

--- a/data/nzd0139/nzd0139.xlsx
+++ b/data/nzd0139/nzd0139.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH269"/>
+  <dimension ref="A1:AH271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -29421,6 +29421,222 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="n">
+        <v>374.17</v>
+      </c>
+      <c r="C270" t="n">
+        <v>367.02</v>
+      </c>
+      <c r="D270" t="n">
+        <v>360.88</v>
+      </c>
+      <c r="E270" t="n">
+        <v>368.43</v>
+      </c>
+      <c r="F270" t="n">
+        <v>365.32</v>
+      </c>
+      <c r="G270" t="n">
+        <v>355.7</v>
+      </c>
+      <c r="H270" t="n">
+        <v>369</v>
+      </c>
+      <c r="I270" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="J270" t="n">
+        <v>381.18</v>
+      </c>
+      <c r="K270" t="n">
+        <v>384.04</v>
+      </c>
+      <c r="L270" t="n">
+        <v>381.23</v>
+      </c>
+      <c r="M270" t="n">
+        <v>386.88</v>
+      </c>
+      <c r="N270" t="n">
+        <v>383.54</v>
+      </c>
+      <c r="O270" t="n">
+        <v>379.95</v>
+      </c>
+      <c r="P270" t="n">
+        <v>378.18</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>377.76</v>
+      </c>
+      <c r="R270" t="n">
+        <v>376.02</v>
+      </c>
+      <c r="S270" t="n">
+        <v>378.23</v>
+      </c>
+      <c r="T270" t="n">
+        <v>378.44</v>
+      </c>
+      <c r="U270" t="n">
+        <v>378.36</v>
+      </c>
+      <c r="V270" t="n">
+        <v>376.5</v>
+      </c>
+      <c r="W270" t="n">
+        <v>379.83</v>
+      </c>
+      <c r="X270" t="n">
+        <v>379.08</v>
+      </c>
+      <c r="Y270" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="Z270" t="n">
+        <v>385.31</v>
+      </c>
+      <c r="AA270" t="n">
+        <v>380.88</v>
+      </c>
+      <c r="AB270" t="n">
+        <v>383.66</v>
+      </c>
+      <c r="AC270" t="n">
+        <v>385.88</v>
+      </c>
+      <c r="AD270" t="n">
+        <v>384.02</v>
+      </c>
+      <c r="AE270" t="n">
+        <v>380.49</v>
+      </c>
+      <c r="AF270" t="n">
+        <v>395.77</v>
+      </c>
+      <c r="AG270" t="n">
+        <v>376.79</v>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="n">
+        <v>372.15</v>
+      </c>
+      <c r="C271" t="n">
+        <v>366.4</v>
+      </c>
+      <c r="D271" t="n">
+        <v>360.47</v>
+      </c>
+      <c r="E271" t="n">
+        <v>366.47</v>
+      </c>
+      <c r="F271" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="G271" t="n">
+        <v>357.81</v>
+      </c>
+      <c r="H271" t="n">
+        <v>371.43</v>
+      </c>
+      <c r="I271" t="n">
+        <v>385.52</v>
+      </c>
+      <c r="J271" t="n">
+        <v>378.53</v>
+      </c>
+      <c r="K271" t="n">
+        <v>382.02</v>
+      </c>
+      <c r="L271" t="n">
+        <v>380.15</v>
+      </c>
+      <c r="M271" t="n">
+        <v>385.66</v>
+      </c>
+      <c r="N271" t="n">
+        <v>382.68</v>
+      </c>
+      <c r="O271" t="n">
+        <v>379.2</v>
+      </c>
+      <c r="P271" t="n">
+        <v>377.44</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>377.48</v>
+      </c>
+      <c r="R271" t="n">
+        <v>375.22</v>
+      </c>
+      <c r="S271" t="n">
+        <v>378.01</v>
+      </c>
+      <c r="T271" t="n">
+        <v>377.85</v>
+      </c>
+      <c r="U271" t="n">
+        <v>377.91</v>
+      </c>
+      <c r="V271" t="n">
+        <v>376.6</v>
+      </c>
+      <c r="W271" t="n">
+        <v>380.11</v>
+      </c>
+      <c r="X271" t="n">
+        <v>379.52</v>
+      </c>
+      <c r="Y271" t="n">
+        <v>379.28</v>
+      </c>
+      <c r="Z271" t="n">
+        <v>385.62</v>
+      </c>
+      <c r="AA271" t="n">
+        <v>381.18</v>
+      </c>
+      <c r="AB271" t="n">
+        <v>384.27</v>
+      </c>
+      <c r="AC271" t="n">
+        <v>387.05</v>
+      </c>
+      <c r="AD271" t="n">
+        <v>384.58</v>
+      </c>
+      <c r="AE271" t="n">
+        <v>379.77</v>
+      </c>
+      <c r="AF271" t="n">
+        <v>395.6</v>
+      </c>
+      <c r="AG271" t="n">
+        <v>376.79</v>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -29432,7 +29648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B275"/>
+  <dimension ref="A1:B277"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32185,6 +32401,26 @@
       </c>
       <c r="B275" t="n">
         <v>0.19</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B276" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:00:00+00:00</t>
+        </is>
+      </c>
+      <c r="B277" t="n">
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -32353,28 +32589,28 @@
         <v>0.0635</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1630284253132006</v>
+        <v>-0.1669299888571913</v>
       </c>
       <c r="J2" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K2" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L2" t="n">
-        <v>0.02980127859344261</v>
+        <v>0.03164521153508915</v>
       </c>
       <c r="M2" t="n">
-        <v>5.564639357690011</v>
+        <v>5.544804805960147</v>
       </c>
       <c r="N2" t="n">
-        <v>47.48644517363163</v>
+        <v>47.18819435989133</v>
       </c>
       <c r="O2" t="n">
-        <v>6.891040935419817</v>
+        <v>6.869366372518744</v>
       </c>
       <c r="P2" t="n">
-        <v>380.2117747043774</v>
+        <v>380.2547158215299</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -32431,28 +32667,28 @@
         <v>0.08699999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.2300032330063237</v>
+        <v>-0.2317588051657254</v>
       </c>
       <c r="J3" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K3" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05688392323199176</v>
+        <v>0.05855799470948608</v>
       </c>
       <c r="M3" t="n">
-        <v>5.526032094957987</v>
+        <v>5.492948866107559</v>
       </c>
       <c r="N3" t="n">
-        <v>48.80901893400768</v>
+        <v>48.45358547222926</v>
       </c>
       <c r="O3" t="n">
-        <v>6.986345177130005</v>
+        <v>6.960860972051464</v>
       </c>
       <c r="P3" t="n">
-        <v>374.1055062476432</v>
+        <v>374.1246460063974</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -32509,28 +32745,28 @@
         <v>0.0733</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3681459705526897</v>
+        <v>-0.3684081079230943</v>
       </c>
       <c r="J4" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K4" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="L4" t="n">
-        <v>0.09660869867427979</v>
+        <v>0.09813170663584769</v>
       </c>
       <c r="M4" t="n">
-        <v>6.499838615801806</v>
+        <v>6.452227817540248</v>
       </c>
       <c r="N4" t="n">
-        <v>69.55317611910127</v>
+        <v>69.02878917778898</v>
       </c>
       <c r="O4" t="n">
-        <v>8.339854682133332</v>
+        <v>8.30835658706275</v>
       </c>
       <c r="P4" t="n">
-        <v>370.7486781261704</v>
+        <v>370.7515642753612</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -32587,28 +32823,28 @@
         <v>0.051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.6087355779897102</v>
+        <v>-0.6098286641762579</v>
       </c>
       <c r="J5" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K5" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1623176466275694</v>
+        <v>0.1649733151046497</v>
       </c>
       <c r="M5" t="n">
-        <v>7.912507810762998</v>
+        <v>7.859345579886229</v>
       </c>
       <c r="N5" t="n">
-        <v>104.4013752434612</v>
+        <v>103.6217295041393</v>
       </c>
       <c r="O5" t="n">
-        <v>10.21769911689815</v>
+        <v>10.17947589535627</v>
       </c>
       <c r="P5" t="n">
-        <v>384.5612354381695</v>
+        <v>384.5733265823528</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -32665,28 +32901,28 @@
         <v>0.0312</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.5626121998673065</v>
+        <v>-0.5688863368729349</v>
       </c>
       <c r="J6" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K6" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1095680445192635</v>
+        <v>0.1132313260348826</v>
       </c>
       <c r="M6" t="n">
-        <v>9.238953654339731</v>
+        <v>9.200259442996575</v>
       </c>
       <c r="N6" t="n">
-        <v>141.5970157806165</v>
+        <v>140.6833923873274</v>
       </c>
       <c r="O6" t="n">
-        <v>11.89945443205765</v>
+        <v>11.86100300932967</v>
       </c>
       <c r="P6" t="n">
-        <v>383.3421188464407</v>
+        <v>383.410964991054</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -32743,28 +32979,28 @@
         <v>0.021</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.6709353087226135</v>
+        <v>-0.6835222476161795</v>
       </c>
       <c r="J7" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K7" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L7" t="n">
-        <v>0.05269148731253492</v>
+        <v>0.05533957664990197</v>
       </c>
       <c r="M7" t="n">
-        <v>16.66462705141598</v>
+        <v>16.61783465522402</v>
       </c>
       <c r="N7" t="n">
-        <v>442.4898724108945</v>
+        <v>439.6907145201912</v>
       </c>
       <c r="O7" t="n">
-        <v>21.03544324255837</v>
+        <v>20.96880336404992</v>
       </c>
       <c r="P7" t="n">
-        <v>383.368649690557</v>
+        <v>383.5076455915167</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -32825,28 +33061,28 @@
         <v>0.016</v>
       </c>
       <c r="I8" t="n">
-        <v>0.4584659182483625</v>
+        <v>0.449366645861092</v>
       </c>
       <c r="J8" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K8" t="n">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0320537123733543</v>
+        <v>0.03128434411469483</v>
       </c>
       <c r="M8" t="n">
-        <v>14.64652792229487</v>
+        <v>14.57535432240405</v>
       </c>
       <c r="N8" t="n">
-        <v>350.175911313369</v>
+        <v>347.7919127935432</v>
       </c>
       <c r="O8" t="n">
-        <v>18.71298777088707</v>
+        <v>18.64917994962629</v>
       </c>
       <c r="P8" t="n">
-        <v>364.0907748637327</v>
+        <v>364.1909855515411</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -32907,28 +33143,28 @@
         <v>0.0266</v>
       </c>
       <c r="I9" t="n">
-        <v>0.638001947078436</v>
+        <v>0.6353513321522682</v>
       </c>
       <c r="J9" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K9" t="n">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1238320846388387</v>
+        <v>0.1246231729034092</v>
       </c>
       <c r="M9" t="n">
-        <v>9.992529212248515</v>
+        <v>9.928268970220012</v>
       </c>
       <c r="N9" t="n">
-        <v>162.3677187618482</v>
+        <v>161.16280953526</v>
       </c>
       <c r="O9" t="n">
-        <v>12.7423592306075</v>
+        <v>12.69499151379236</v>
       </c>
       <c r="P9" t="n">
-        <v>370.2074128001746</v>
+        <v>370.2361164638808</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -32989,28 +33225,28 @@
         <v>0.0515</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4159515863836759</v>
+        <v>0.4097000094681671</v>
       </c>
       <c r="J10" t="n">
+        <v>270</v>
+      </c>
+      <c r="K10" t="n">
         <v>268</v>
       </c>
-      <c r="K10" t="n">
-        <v>266</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.1112301416057765</v>
+        <v>0.1096101634712709</v>
       </c>
       <c r="M10" t="n">
-        <v>6.893663430420591</v>
+        <v>6.87133558548022</v>
       </c>
       <c r="N10" t="n">
-        <v>77.72742796465295</v>
+        <v>77.2998825642084</v>
       </c>
       <c r="O10" t="n">
-        <v>8.816316008665577</v>
+        <v>8.792035177602989</v>
       </c>
       <c r="P10" t="n">
-        <v>373.042319507967</v>
+        <v>373.1098760744332</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -33067,28 +33303,28 @@
         <v>0.0655</v>
       </c>
       <c r="I11" t="n">
-        <v>0.3744774704651547</v>
+        <v>0.3730526115037295</v>
       </c>
       <c r="J11" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K11" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1204357492453187</v>
+        <v>0.1212880169059463</v>
       </c>
       <c r="M11" t="n">
-        <v>6.031089250255714</v>
+        <v>5.992626835078831</v>
       </c>
       <c r="N11" t="n">
-        <v>56.35413745624919</v>
+        <v>55.94515211296563</v>
       </c>
       <c r="O11" t="n">
-        <v>7.506939286836492</v>
+        <v>7.47964919718603</v>
       </c>
       <c r="P11" t="n">
-        <v>373.9368314153491</v>
+        <v>373.9524744512332</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -33145,28 +33381,28 @@
         <v>0.07770000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.4100807255821205</v>
+        <v>0.4074737240205467</v>
       </c>
       <c r="J12" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K12" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1467063147058011</v>
+        <v>0.1470411799543323</v>
       </c>
       <c r="M12" t="n">
-        <v>5.937713071437148</v>
+        <v>5.905924893805241</v>
       </c>
       <c r="N12" t="n">
-        <v>53.82086901071844</v>
+        <v>53.44190595067515</v>
       </c>
       <c r="O12" t="n">
-        <v>7.336270783628317</v>
+        <v>7.310397113062679</v>
       </c>
       <c r="P12" t="n">
-        <v>371.4553400507476</v>
+        <v>371.4839513698316</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -33223,28 +33459,28 @@
         <v>0.0945</v>
       </c>
       <c r="I13" t="n">
-        <v>0.3092331400897142</v>
+        <v>0.3130531467745455</v>
       </c>
       <c r="J13" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K13" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1173511240629461</v>
+        <v>0.1214627949800369</v>
       </c>
       <c r="M13" t="n">
-        <v>5.037338376027836</v>
+        <v>5.019352004400647</v>
       </c>
       <c r="N13" t="n">
-        <v>39.57628699334884</v>
+        <v>39.33205801612628</v>
       </c>
       <c r="O13" t="n">
-        <v>6.290968684817057</v>
+        <v>6.27152756640089</v>
       </c>
       <c r="P13" t="n">
-        <v>375.3310461314438</v>
+        <v>375.2891330889327</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -33301,28 +33537,28 @@
         <v>0.0839</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1390773547430631</v>
+        <v>0.14100800325164</v>
       </c>
       <c r="J14" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K14" t="n">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03759858124849902</v>
+        <v>0.0391831835558496</v>
       </c>
       <c r="M14" t="n">
-        <v>4.21522317514699</v>
+        <v>4.19526932641955</v>
       </c>
       <c r="N14" t="n">
-        <v>27.41063777108068</v>
+        <v>27.21969902496007</v>
       </c>
       <c r="O14" t="n">
-        <v>5.235516953566351</v>
+        <v>5.217250140156217</v>
       </c>
       <c r="P14" t="n">
-        <v>378.036722581963</v>
+        <v>378.0156471990962</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -33379,28 +33615,28 @@
         <v>0.0854</v>
       </c>
       <c r="I15" t="n">
-        <v>0.2808577972963023</v>
+        <v>0.2779681241652838</v>
       </c>
       <c r="J15" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K15" t="n">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1685399060435334</v>
+        <v>0.1676513800482173</v>
       </c>
       <c r="M15" t="n">
-        <v>3.718181443333791</v>
+        <v>3.700559653963178</v>
       </c>
       <c r="N15" t="n">
-        <v>22.0042636776688</v>
+        <v>21.87169780214652</v>
       </c>
       <c r="O15" t="n">
-        <v>4.690870247370823</v>
+        <v>4.67671870034392</v>
       </c>
       <c r="P15" t="n">
-        <v>374.0584010438703</v>
+        <v>374.0894727440389</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -33457,28 +33693,28 @@
         <v>0.08069999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1675877977416821</v>
+        <v>0.1654907582062269</v>
       </c>
       <c r="J16" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K16" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08278357595319918</v>
+        <v>0.08199989753624959</v>
       </c>
       <c r="M16" t="n">
-        <v>3.499203335992612</v>
+        <v>3.482255932654551</v>
       </c>
       <c r="N16" t="n">
-        <v>17.56503982070706</v>
+        <v>17.45166347837281</v>
       </c>
       <c r="O16" t="n">
-        <v>4.191066668606819</v>
+        <v>4.177518818434312</v>
       </c>
       <c r="P16" t="n">
-        <v>374.7791035151135</v>
+        <v>374.8016488710452</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -33535,28 +33771,28 @@
         <v>0.1562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1997481465727598</v>
+        <v>0.1994283590880423</v>
       </c>
       <c r="J17" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K17" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1058804079023793</v>
+        <v>0.1070739753460962</v>
       </c>
       <c r="M17" t="n">
-        <v>3.489103890128492</v>
+        <v>3.464755255498189</v>
       </c>
       <c r="N17" t="n">
-        <v>19.01876150887069</v>
+        <v>18.87840522314316</v>
       </c>
       <c r="O17" t="n">
-        <v>4.361050505196046</v>
+        <v>4.344928678717657</v>
       </c>
       <c r="P17" t="n">
-        <v>372.4738953842699</v>
+        <v>372.4773340995496</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -33613,28 +33849,28 @@
         <v>0.09279999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1368080923793877</v>
+        <v>0.133290573485783</v>
       </c>
       <c r="J18" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K18" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04791941065924998</v>
+        <v>0.04619329454120236</v>
       </c>
       <c r="M18" t="n">
-        <v>3.675387795141954</v>
+        <v>3.662222591020118</v>
       </c>
       <c r="N18" t="n">
-        <v>20.99048762476536</v>
+        <v>20.880467848058</v>
       </c>
       <c r="O18" t="n">
-        <v>4.581537692169012</v>
+        <v>4.569515056114598</v>
       </c>
       <c r="P18" t="n">
-        <v>374.4166051299916</v>
+        <v>374.4544205149553</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -33691,28 +33927,28 @@
         <v>0.0859</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1387555304235288</v>
+        <v>0.1353546391273588</v>
       </c>
       <c r="J19" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K19" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L19" t="n">
-        <v>0.04585834904708663</v>
+        <v>0.04432137865198971</v>
       </c>
       <c r="M19" t="n">
-        <v>3.709957895260437</v>
+        <v>3.691245851931879</v>
       </c>
       <c r="N19" t="n">
-        <v>22.61162389771398</v>
+        <v>22.48561751684237</v>
       </c>
       <c r="O19" t="n">
-        <v>4.75516812507339</v>
+        <v>4.741900201063111</v>
       </c>
       <c r="P19" t="n">
-        <v>376.7849009841709</v>
+        <v>376.8214605073709</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -33769,28 +34005,28 @@
         <v>0.08169999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>0.106737589198185</v>
+        <v>0.1031192392532587</v>
       </c>
       <c r="J20" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K20" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L20" t="n">
-        <v>0.02899418079644622</v>
+        <v>0.02747408289139741</v>
       </c>
       <c r="M20" t="n">
-        <v>3.661479473794754</v>
+        <v>3.648538396972704</v>
       </c>
       <c r="N20" t="n">
-        <v>21.53686468202043</v>
+        <v>21.42482577065721</v>
       </c>
       <c r="O20" t="n">
-        <v>4.640782766088112</v>
+        <v>4.628695903886667</v>
       </c>
       <c r="P20" t="n">
-        <v>377.8225149424106</v>
+        <v>377.861413442088</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -33847,28 +34083,28 @@
         <v>0.1406</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1553485407478193</v>
+        <v>0.1541535883370289</v>
       </c>
       <c r="J21" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K21" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L21" t="n">
-        <v>0.05871340697835936</v>
+        <v>0.05871790043976322</v>
       </c>
       <c r="M21" t="n">
-        <v>3.661992136940862</v>
+        <v>3.64009346509699</v>
       </c>
       <c r="N21" t="n">
-        <v>21.83914629580255</v>
+        <v>21.6828555754457</v>
       </c>
       <c r="O21" t="n">
-        <v>4.673237239409374</v>
+        <v>4.656485324302622</v>
       </c>
       <c r="P21" t="n">
-        <v>374.7975011117557</v>
+        <v>374.8103482013818</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -33925,28 +34161,28 @@
         <v>0.0867</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2127413472423596</v>
+        <v>0.208377758061485</v>
       </c>
       <c r="J22" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K22" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0917272608516333</v>
+        <v>0.08938985143231826</v>
       </c>
       <c r="M22" t="n">
-        <v>4.07451305974072</v>
+        <v>4.064397676476082</v>
       </c>
       <c r="N22" t="n">
-        <v>25.29637993468697</v>
+        <v>25.17716994636675</v>
       </c>
       <c r="O22" t="n">
-        <v>5.029550669263307</v>
+        <v>5.017685716180991</v>
       </c>
       <c r="P22" t="n">
-        <v>373.8996009412479</v>
+        <v>373.9465080191769</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -34003,28 +34239,28 @@
         <v>0.0853</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1946299300922934</v>
+        <v>0.1917865137133296</v>
       </c>
       <c r="J23" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K23" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L23" t="n">
-        <v>0.08413954689076375</v>
+        <v>0.08299732885729372</v>
       </c>
       <c r="M23" t="n">
-        <v>3.925863145029535</v>
+        <v>3.911001383262452</v>
       </c>
       <c r="N23" t="n">
-        <v>23.27475410267154</v>
+        <v>23.13143271750169</v>
       </c>
       <c r="O23" t="n">
-        <v>4.824391578496872</v>
+        <v>4.809514811028415</v>
       </c>
       <c r="P23" t="n">
-        <v>376.7362522187404</v>
+        <v>376.7668171684106</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -34081,28 +34317,28 @@
         <v>0.0852</v>
       </c>
       <c r="I24" t="n">
-        <v>0.1845504535849491</v>
+        <v>0.1814356657231627</v>
       </c>
       <c r="J24" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K24" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L24" t="n">
-        <v>0.06660515244121246</v>
+        <v>0.06539837158710027</v>
       </c>
       <c r="M24" t="n">
-        <v>4.121431911405684</v>
+        <v>4.105995052600007</v>
       </c>
       <c r="N24" t="n">
-        <v>26.94167028291633</v>
+        <v>26.77718027390274</v>
       </c>
       <c r="O24" t="n">
-        <v>5.190536608378398</v>
+        <v>5.174667165519222</v>
       </c>
       <c r="P24" t="n">
-        <v>376.5307507174499</v>
+        <v>376.5642322636924</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -34159,28 +34395,28 @@
         <v>0.0835</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1761299579233858</v>
+        <v>0.1734878407465474</v>
       </c>
       <c r="J25" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K25" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L25" t="n">
-        <v>0.06345936709845679</v>
+        <v>0.06254876613092042</v>
       </c>
       <c r="M25" t="n">
-        <v>3.997513532705304</v>
+        <v>3.979955453821684</v>
       </c>
       <c r="N25" t="n">
-        <v>25.84247240311252</v>
+        <v>25.67603387793378</v>
       </c>
       <c r="O25" t="n">
-        <v>5.083549193537181</v>
+        <v>5.067152442736826</v>
       </c>
       <c r="P25" t="n">
-        <v>376.3888452567579</v>
+        <v>376.4172472252523</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -34237,28 +34473,28 @@
         <v>0.0989</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1447245390153295</v>
+        <v>0.1462251900641235</v>
       </c>
       <c r="J26" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K26" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05101893583453321</v>
+        <v>0.052791944541418</v>
       </c>
       <c r="M26" t="n">
-        <v>3.708094582547649</v>
+        <v>3.68871718488098</v>
       </c>
       <c r="N26" t="n">
-        <v>21.99111304947839</v>
+        <v>21.83644978275273</v>
       </c>
       <c r="O26" t="n">
-        <v>4.689468312024125</v>
+        <v>4.67294872460128</v>
       </c>
       <c r="P26" t="n">
-        <v>380.5158390490193</v>
+        <v>380.4997063001401</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -34315,28 +34551,28 @@
         <v>0.096</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1046858873791875</v>
+        <v>0.1007761222881867</v>
       </c>
       <c r="J27" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K27" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L27" t="n">
-        <v>0.02568665537079917</v>
+        <v>0.02416323563376976</v>
       </c>
       <c r="M27" t="n">
-        <v>3.872629329554486</v>
+        <v>3.860869072623595</v>
       </c>
       <c r="N27" t="n">
-        <v>23.46410966637649</v>
+        <v>23.34518350896241</v>
       </c>
       <c r="O27" t="n">
-        <v>4.843976637678643</v>
+        <v>4.831685369409147</v>
       </c>
       <c r="P27" t="n">
-        <v>380.9698000205578</v>
+        <v>381.0118278643434</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -34393,28 +34629,28 @@
         <v>0.08599999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>0.1444323919510855</v>
+        <v>0.1405542568638791</v>
       </c>
       <c r="J28" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K28" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L28" t="n">
-        <v>0.03766773453060279</v>
+        <v>0.03622743322516031</v>
       </c>
       <c r="M28" t="n">
-        <v>4.482160082027202</v>
+        <v>4.462916299360028</v>
       </c>
       <c r="N28" t="n">
-        <v>30.08302218667712</v>
+        <v>29.91471851379179</v>
       </c>
       <c r="O28" t="n">
-        <v>5.484799192921936</v>
+        <v>5.469434935511327</v>
       </c>
       <c r="P28" t="n">
-        <v>382.8075041701213</v>
+        <v>382.849190836199</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -34471,28 +34707,28 @@
         <v>0.0856</v>
       </c>
       <c r="I29" t="n">
-        <v>0.17914258488615</v>
+        <v>0.1717838521650768</v>
       </c>
       <c r="J29" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K29" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L29" t="n">
-        <v>0.06215499510647671</v>
+        <v>0.05790636594401688</v>
       </c>
       <c r="M29" t="n">
-        <v>4.320541882129962</v>
+        <v>4.322426332573668</v>
       </c>
       <c r="N29" t="n">
-        <v>27.3331331103238</v>
+        <v>27.32702485276305</v>
       </c>
       <c r="O29" t="n">
-        <v>5.228109898455062</v>
+        <v>5.227525691258059</v>
       </c>
       <c r="P29" t="n">
-        <v>386.8230822619572</v>
+        <v>386.9021823925397</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -34549,28 +34785,28 @@
         <v>0.1127</v>
       </c>
       <c r="I30" t="n">
-        <v>0.2001635339707055</v>
+        <v>0.1918707137795344</v>
       </c>
       <c r="J30" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K30" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L30" t="n">
-        <v>0.1028711134962443</v>
+        <v>0.09560032700588061</v>
       </c>
       <c r="M30" t="n">
-        <v>3.531402399515127</v>
+        <v>3.538472371442509</v>
       </c>
       <c r="N30" t="n">
-        <v>19.72277546377347</v>
+        <v>19.82340800347614</v>
       </c>
       <c r="O30" t="n">
-        <v>4.441033152744243</v>
+        <v>4.45234859411032</v>
       </c>
       <c r="P30" t="n">
-        <v>384.7524814053068</v>
+        <v>384.8416250023385</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -34627,28 +34863,28 @@
         <v>0.08450000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1480299110082204</v>
+        <v>0.1373825763869402</v>
       </c>
       <c r="J31" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K31" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L31" t="n">
-        <v>0.05351354770964312</v>
+        <v>0.04631403668859813</v>
       </c>
       <c r="M31" t="n">
-        <v>3.818059510042123</v>
+        <v>3.835081654479541</v>
       </c>
       <c r="N31" t="n">
-        <v>21.87692736036041</v>
+        <v>22.12157207184366</v>
       </c>
       <c r="O31" t="n">
-        <v>4.677277772418527</v>
+        <v>4.703357531789782</v>
       </c>
       <c r="P31" t="n">
-        <v>383.6368357541767</v>
+        <v>383.7512944996889</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -34705,28 +34941,28 @@
         <v>0.06909999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>0.193101751899338</v>
+        <v>0.1861765647558328</v>
       </c>
       <c r="J32" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K32" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L32" t="n">
-        <v>0.08105989805854252</v>
+        <v>0.0763840888913041</v>
       </c>
       <c r="M32" t="n">
-        <v>3.795600923775449</v>
+        <v>3.799545161331268</v>
       </c>
       <c r="N32" t="n">
-        <v>23.86109057194438</v>
+        <v>23.85604508698677</v>
       </c>
       <c r="O32" t="n">
-        <v>4.884781527555186</v>
+        <v>4.884265050853278</v>
       </c>
       <c r="P32" t="n">
-        <v>395.3645172011804</v>
+        <v>395.4389617983194</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -34783,28 +35019,28 @@
         <v>0.0289</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1298902181564372</v>
+        <v>0.1232321774193578</v>
       </c>
       <c r="J33" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K33" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="L33" t="n">
-        <v>0.02168123287903634</v>
+        <v>0.01979053410589482</v>
       </c>
       <c r="M33" t="n">
-        <v>4.760610404213618</v>
+        <v>4.76043228811345</v>
       </c>
       <c r="N33" t="n">
-        <v>42.9720441536019</v>
+        <v>42.81239660469705</v>
       </c>
       <c r="O33" t="n">
-        <v>6.555306564425641</v>
+        <v>6.543118263083517</v>
       </c>
       <c r="P33" t="n">
-        <v>377.9824737691529</v>
+        <v>378.0540459671916</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -34842,7 +35078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH269"/>
+  <dimension ref="A1:AH271"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -80861,6 +81097,350 @@
         </is>
       </c>
     </row>
+    <row r="270">
+      <c r="A270" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-02 22:04:43+00:00</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>-36.588762996917694,175.52482643186048</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>-36.58912884496742,175.5240580886446</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>-36.589654311498116,175.5234618546301</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>-36.59027389981434,175.5230317173697</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>-36.59095378963801,175.52278235832355</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-36.59164569520016,175.5225001234819</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-36.592364872162086,175.5226822417171</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>-36.59305200159465,175.52289744578582</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>-36.59373000070341,175.52307727667375</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>-36.59439128752565,175.523377357886</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>-36.59504430589834,175.5237101012403</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>-36.59564923178044,175.52416473769537</t>
+        </is>
+      </c>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>-36.59625874256238,175.52460223521862</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>-36.596847635642206,175.52509309405096</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>-36.597395408215284,175.52565608140034</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>-36.597920890093846,175.52626524179027</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>-36.59846812305531,175.52685305528652</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>-36.5989822184912,175.52747500630795</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>-36.59948338375347,175.52810778687945</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>-36.59996914443403,175.52876643625459</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>-36.600468989648355,175.5294148506175</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>-36.600929364315064,175.53009500256164</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>-36.60137027694259,175.53078638103068</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>-36.60178192225332,175.53151774214427</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>-36.60214626857416,175.53227985346808</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>-36.60253530931605,175.5330203667161</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>-36.602856330843316,175.53381362981344</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>-36.603141149123076,175.53460989561827</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>-36.60337173376205,175.53543140271316</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>-36.603580687835965,175.53628294315843</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>-36.60361352894106,175.5370590867688</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>-36.603513086955076,175.53784856077914</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:04:54+00:00</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>-36.58874847209013,175.52481283475294</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>-36.58912490512186,175.52405317844955</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>-36.58965219343883,175.52345810186821</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>-36.59026695918828,175.5230115821098</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>-36.59094865958703,175.52275150121113</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>-36.59164685701442,175.52252365331654</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>-36.59236364157263,175.5227093481347</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>-36.59305200159465,175.52289744578582</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>-36.59373720784309,175.5230490500922</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>-36.59439813822159,175.52335644881785</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>-36.595048667174694,175.5236993144811</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>-36.59565483989242,175.52415301438978</t>
+        </is>
+      </c>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>-36.596263227690216,175.52459439994846</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>-36.5968519396518,175.52508663406238</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>-36.597399952916994,175.5256500319312</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>-36.597922628658274,175.526262974909</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>-36.59847306048586,175.52684654337565</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>-36.59898361658224,175.52747326386762</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>-36.599487290896235,175.52810331710177</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>-36.59997217755316,175.52876309988483</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>-36.60046831561939,175.5294155920337</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>-36.60092741125425,175.53009698273874</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>-36.601367052944305,175.5307892416831</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>-36.60178169869362,175.5315179305343</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>-36.6021438899006,175.53228166873348</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>-36.60253293196785,175.53302196148115</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>-36.60285139969192,175.5338166389407</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>-36.60313129256589,175.53461452952124</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>-36.603366864673,175.53543304167496</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>-36.603587004512214,175.53628111316763</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>-36.60361505255455,175.53705928030618</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>-36.603513086955076,175.53784856077914</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
